--- a/.qc-agent/ground-truth/test-cases.xlsx
+++ b/.qc-agent/ground-truth/test-cases.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>b4e5c1f22558a2e7fc4bdc834cf286aea1e54f6e28ab5e6f7cbe1f7e0d5444d9</t>
+          <t>e06f1d34178ed9cec7d4cbce16894f75b8157803617b0e2be778fe92688d4562</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>eNrtXeuPG1WW/1dK1koQjR2Xy+VXVvshk2RJdgPJJA0LM0Kt66pr16XLVaYeTpso0iA+oNUIMRE7GiGEhtCKosBEwGQQmm6N+OBs/o+ev2TPOfdW+Za7bHeHJrNSjMD4Uafuefzued1bt29XnDAY+MJJ4sq523eqlXHkwpuKgNfKhHksqFQrscesVhu+aA9si3G3z1tN0+70BoOm3ej32KDvNHnftru9jtW3+4Mec1p9p2HZcKnb6NoWHzgDp+t2KzBAnLAkhcEqbsQGCdw94XGy7bCYIweVrQu18xdqjbONWmvQbVsD/I452xEfwM+/qcjfKm9XK3wiXB44HL6FTzsiQI7ZWGwP0sBJRBgwH24ehAneN0h9v1oJIzEUAVzm+6MKispBeFfgxfk140jAZck0+xwxeS+ef8Hf4U7CXWCJxWGQfX1ErDjhY2T5doXvjoECBXmHCOCrcAxXBhyZYIkH7/8F3k6Yn6ph7rw9v+NvbLNRtS3r7Ts4+LspqGt+r9twgzi+FaLVKreiMBji54bVhPulMY8CNuI4VBjwXQEsBck2fr29O30PjTHiiRci6fVrN7fm3NRBj3WWJl7dD1Fjd5CfhDteIN5Nc00kIkG1VJ78/skHwdAIvMP9R2NjcnjwmTCysesZe0bMhNE/PPidkRwefG043uHBXYEsZAa3anar0Wg2ygxuAWv0pvcCWt5sLrN8FA6Ez6+40sC1zMI19UMFqcacAVElRH3BnR2Pu6nP3fP4pWX2ejWzAf9umeY5+vcXZgdecVaKEX8PUAOXnY8Fq18Oty94YvtVEXjrgBOlQS0bKF6DnVcODz4SxvnrVwAW+/dCwweEOJ4xmn1h7HizvwKsnNljY+yJ2VeBAZjZG+MlH0qwBcux5LTaTtPcYOm4WHL5QAQkwxs8igV+2QC5pfeIvTD13dqACX+d7QF3CY8yBJ7U+pLaUNTGy2jZh44RkH9h7kgEZwAWAiz+9FtmPLmr+51VvqVZG3CbOXYZHpovFgws01yAwNoYwEADE5TiuMbMCIxx6PsCTKSm8nD25RSn7x8FGO3pt/MfnFAYPkx5LwQYJGDYw4NP0bLDp98eHnwuDHf2N/iYeDw0rt+4qFvWrnXMLm+0yixrL7XswA9vvbj2hJgepglYs/pzeZWchVculXIAXmU1lm6ylCa6muK76eH+/aRqJOEOD7JoICe8l2JY+ERkUErg0wfGMMfik7uIoT0HLt/fCzE7+VDHT6vWarpdq1eGn9YmzZwHCCeNIsgtrs+zzdB3s+RO5psBv6X9DEEjSo6VY+YZ7Lo08/DgD8IYgbdPwNqH+w9T+IDJZjA83P8G0oOn9wKjYRk7s79jIPhuZUho1dpmt9+wN4Y/seFjyApWWn7h9+eCgSSiGFH4xRMw2wPKLVbXHu1ap8lYt7TYbL+QaeLxCk64iVhwAlFIhhrxUZ9HxSJ0HRDw0nUZ4xblicnsC3T4kC3sBQsFpxFBfgFAWGXubs3u2y2zNGnobsxdNPdpFYJ1vFGN7nTcPBLzQJjtGQdZcYiJwcricLntrbNQ7YLp2/2jtrdeyL7SSXK3kxV3VyFnmxouCzwjnt0Duy1Udycv5NB6/XbLNHsb6x1j5s5retnaLanxe/BPXua/PnZZAg4UdIi/GtiYLU7x19cgon5bvdsW7h116faYRWwUaw2rbbGsY1UTmACsRJVicgFLMgbknK/uNSKMXMtqNvgGRqcDo3mr6HT7Q1tlXSFp6wR9fhJh4j9cY2ve6vSZu7H1adua/ZP/eb5Ym1AfITHeTWf3oMo0j1NmAsLMGjebbbNZCj9zg7+FpOPipauXti49hyhTrcDg0RQJsrBB4XBN+Hlz9pj9xOBj1RrWAOrNMkRYG0CscEgVB7gNXBa9xVlUOWeZll2tSGNIfgaC+6ismzAAsjAKXTTaQOxyN2ODlD1p4EdcCppg0Tqx8aWFL2186eBLF196+NIw6ZVoGkTUIKoGkTWIrkGEDaJsEGmDaC2iteR4REtl8sQiWotoLaK1iNYiWotom0TbJNqmZJZom0TbJNom0TaJtkm0TaK1idYmWptobSkp0dpEaxOtTbQ20dpE2yLaFtG2iLZFtC2pJqJtEW2LaFtE2yLaNtG2ibZNtG2ibRNtW+qYaNtE2ybaNtF2iLZDtB2i7RBth2g7RNuRBiLaDtF2iLZLtF2i7RJtl2i7RNsl2i7RdqV1ibZLtD2i7RFtj2h7RNsj2h7R9oi2R7Q9CQ2FDQkOE3IJxPbuefA2gLlXwyDx/kvECMNp9h3b4VFlXVi9tOtw7hoSrIYvRiJ5bpFODVqIdUNBP0Fxhu1V01zj3Not3u5unNtPdW6oghqrBanqo/10XF0JqF1nTOH+mdmfG7CCJx+MKDLuAJo+SA338OAbwPbhwYfpGjz1HbPtOBs8nRhPabAThLeCf1cxUd72uCDBtt2IPXeYYMfvd4FnBEPvyUMG/wux06uYWYUTuzbgUOeVptn2BidFnCymSZA7Q3r8hsqObt85mbXr4Viq5DjtQHltZnxsASaeONz/MTWIKdoB8IMDXzJwF2BkXLb9JjH66eHBp85KBHRqzWbbKdswCL9tEHAaafXrQZyOx2EEwpBXefOtX69KstlpZUTauAomUfocnZIcUq04AO7+iH2ng701aLS5OWjxDRpPBY1OOOqLgGS5QbsKy6o9UDJgZyvUvkqmYzQujikiQMypwPEm9wdQ7g+eLwo1FdDAsvdEjtJRLnQ5IJtnG7Wu6TJekkg1N23QVTtr43DET7Cj1jL/yTtqt/R9tKp/6dEuuqFggSzpdnBf5Rq49JomL9ses4HLacLlyAbsnw0KWZ6Vr6avMr9VazWanbIdEs1N2fVzmv8XZutcc8FbXEqjcMzrV0FbMODP7CoydJwk3UG8dK2uaQ82eDklvLhM+NP/jw9slGBGMp13dpDzlWDp1ey2yVmvDCy9FxQspg3/9U68MlbcYXU7e1u+MKb9urgylv10jA0YtAKW78SSe64PDz7JtlmqAl79gv2cB/AK0Hg/JYR8GKzAhg15h9UY8EFJmmpv8o7j7PAHRAQ8qsO1Ka87PhOjNRP6Al5j4POXSzbWyTseb3+dfbZZ63Y7vKwRZ79oj9qsjwQgRhIxJ8mLTLkw+U7YP/pQH3y5dgOtqHmc+bidGvTui6GXrDH+9ew65cphkLJJvcrgrZprsVbbLjN4a2PwBYOzceJ47Ip6fqIG732fB0NyvM9ueDXpQyeqAzPROqv/knqq4Jv3H6TGtQs3sg5Dxlw9Z8tw/vdh5tJPjI0W7bNrO2ZJF6y18ebH8eZ9BhapSWce8xidBIZ5+Q6jfH3M0piXxPr8kiOhXv5yjEh/HW9tqOtPanqrZrX7zZ5VZvpNRXAqpo94nI5+JtvfoHs/m/Hb2D3q9xtmifHbm3l/nIckgyBlfg0KqzBK4oq2V81lCWRqWAtOuCccrNeqlWneKV+Xu/OR0Z9B/ebgy3wD/kkfo2iftWtmz2kzs8zCm/XWU7fwmA05LUHgm5viPfwAwx7f8m/NvkoNhwL+2Jt9iVunGUzo4qZW0zTc2V+CYV3+uGj/LBHQNwTpmGjXeo225TbKMNF+gev6Z8dFHfjAp2jXwSOm5a5zlZvhiGdLX8eGxiUaQy06cVc+Zk93BMAc3FdPVONW+z1MFN8v7N3BlYTPxgsVvg6KTq3ZMLtWuwwUL+pC6OpGz2mB4qQAgJQ/XyTAQ6FENDrv+/+WROmRzgBhrH5j6xokCCzCxYU5OuT5Druze446pEVHQw8Kgka7XYqG3sZFnA4a5sarnBswP+bV1V7jtTC4pDJEMuybb/1aPsv7zC5EgwoFlMxNaDABsefA6EDG2LG6TVay4NTZPJZ5MkBgT9gDc4bRuhNbbqSBcVleSSH+v+UZO8YuH1UN+QR3FvNP9qBmB8/V6DhN3iyzZ2tz4s5SW85beIp+zdOQV4zLdDlNrXt0/snsntAnWqJKN7CrK9gwCONEOLFuq07N7Fidvl1mq85m7q05zsYV69ptdCQSXleYZBBXp5iRPxpXn/Vp9i4edNbstFjnqOm6L1qX5UTTDLhy13nHS4E7DkWQGHixCHgcF6ZVYb7Fh/vfB0Y8+yIY4rlKFVBuOMFQiHzIZ/2gLKq8MXuE2fN93N+MmfKIzi+azmszPbXGvPs7B7stP0rzv3H+8vnXoFRj2ZLMy5iBUbqOvwMzFL7P6KfnqeSdtorRyi2SX97aum44mO/RSVsO4IxgOPZkvi83205mX4QFhoJhSv0fuSv7rDxHzzrbRMHwCkffLUDd5alaAHQwG/RD6hvJ3ZRaZYGSB3L1eIRlKbHoQMLihxBqgBXqNX2K/BxDP/8KQ9IxY3D1CMgSeXli7My+kocRwLf3HRz1fmp4sz8Hnj79PDChZ0yE1FGEcxEKYXkH/F2yzOKYQ76jCYHMwcCPac1TnjiVK6hVrL81ScF9R0Dok2Jgsn/HaI5/FGACrg7AoiMwHI/JA9Iy9oaCgXHkeioU9I+A0BeQwFWLhgdVIizvJaRUdEQ8Q7Vu+pxVPOT1cjYG7eitC0jpsBbUUOrJlf5giNZw8BAWr8Teaqv3ehjjPu9gWF2ELB30AlNZrk3q7GZXFvF6DKh251BFfvdG6lSwlwKYxSCEhCLOycTTByIXDC8fG7MvR/Tbg9FLGsQyFpLZI3x4YY5ZoH8sayFw+R4JLbGDmvmPm9dey0CjTdk+lmCJAmgSzfYd8EDxGLyvXpDnMvXmMkmd4ZiIo/Rw/yEEEvxQqq+ENgGSayhAby6Wg9vzFTf4HAbq7IdEl+9lj8WeCIb1IIxGzBfvURw4o88oh87+mAMR3QPiAe87nrujowqIZt+XKkFJ3tQdjzanBsBJdicNs7fCaAew5oQpYH8iBwPNyK8v0Lc+HzJnmtFKWHs4l/+EugtDvzgF8WhcZ8HYy2ae1GduRpIY/MS9AAF9sMb68yFy0e2iS8m2b0TG7uHBI2Dz79kODXf2NyNhfYTZ3txBzf6C7buDjwXZ/PPCBlE1X9HWP0ofpG6lvpHPAaIG5yLmOgFW3w8WZnJum5DO50JFkLrmUSihUz4lE7mIC15TMXENchmoSWA8RPv9RFuZQBjv/zBW3vSokEclUqLGSOugXFNjN0RPpM1sQURgCAwUMtYeVVbx7EGBSYJ0VDm8gyGbqu9I2lxM9Lj/OUev47PRGK6efTE1rF69adabDdWoT6dwVUAJByoSt6/704KcJQaZI2MZ78hi4Mn2nbz3EvtpRsrlysXo4BM+5HOHc1bpoT/plNQWt7rSvPxFugBibK7xdyEtVupWWRKdKX2fvNdD6eTGR6Vx0UERNqt4RiguXOOJo6A58iP5MscAcjyIEhNuZKlxde4eYbLIxBujTVmYPyI3RpSLImZ9n8OtkzTiGNVimh99OotOwjHgu4lBa/NUPd+XLfegYD6SyZ19LxaSS6UzHHtR4mOYCrj4Di7Qcz70O4TSQMlh41EUuTNFpanzlWUzT24PAO6HvO6ELq+7PGHC1xWD9tPCBfjGIR78qnnHkuRSxf8sQwDyfhTeAp0v8yDrIgc1nLQ0QLKvZyC7IPXUiFguuIX1gf6E84hoFGu5O01oAeTJ3cyVU07i0JGDPvpo3Y6j2V9J2o+pVSJnVlFUhNcnSrzPM/0q2WXqAYlcYW0GTzTcUwchK3Xohu37zNmp9cPdcuvaet6DDOVP4BHmjpiGGPzIUdi9eO1VNSHmmUwhEh41INS7STiSD6toGADAPMjSvtzGc6+Vn9W6mKzmgrS1kC+psUjAXAeNhltZsN2xNDOjyk0mJAjyYoGxDHSyICnGbsScShbzMp5u52HFjjeAjDbnulMMZZhz9MNwx5Ct22LqjNpPx37IcCGGFOyonZSao5g9Agmkp5pkp1+iw3TR8X6Y6AaR2XaGqaWBSoZU6k+oPLW8SMxlQsd3nVYSVXX02rXti+e3zuudC8mbmoRixMM0qW9dvVm3TXvphJFXjzL/p9UOlD/QZMii8Vz1JOXClBnjfB4hPpUpVdbFqbvy6bh8qvSK8XiH3Nm7KWoKyp1HQs6JukomRoiugPSlBsGYkohkWi/68GXiRgzymby/UhAYl1m/YQsepCpLChlUCzVRbjNdrGWOkdyXHExJ3qJ0+gZPoqkcWV6TiUO49Kk1JVXCkoSPxpjOo84/K3pAyvuBvI57xnSZKA1VqRbeMZGxsE9+Rr/VY2VvfT5VlzY1yhWhBYZ1wSdXgl00fwZqvQ5EL8XkPSa0uBGR0iRwy7QgpdaT1mzS6gjJhjqK+aIOSkTRpvtcKpjvuVSYS7+ZhTJ1iStiwF3AnUQGgSFCse5zxXApWkcy5SYABBQRixNVZtIFJ3+SKKZ6dwrBKCJ42FwIypTBDkKqAEZjKbplSqrk3xA4+Nq4+aurBfazC3QOIUBNQAPFGqZojXVhoeghZaeGUe5L2O6rcoHOr88jQYsiQd5fQSqpUaVF6atP7hnVIdh6y6O0m1JkOlFJzxxchksTMHeY+PWjnPcunb+c9dZwyr2vDmY3Xn7y+zfPqCQ7iQQl/zseE/mR/dXSHlth7KKbmKtajd+WKao2N6WJ3JS0nmee9MQsHqHjGy8nAoMucVo14nQ0YtG0mp8x4UpN0ikDoNvPgjMF1Y9ZFHN5O0iGYd7TvpkVgC5v7MjZQNkPNbNkNQjl3Vwu7AxfffptXuPGOFNlXKM0XPYroJBzdkAIpRx8vSvyR38h2ca7qwoYL396j8D4YxmU0QrUzCF975X3mrBuirCjXayGytzrk7vhjGIOBWeQYi6cdZy2t9VSO4+WNnjJherbD4+6Rjn/syCyPFgU+oRYZy9MC61PUd5+zIWztM63UMU5IuWlf/z2f14C7YcL4khTTRaaPYHx2utXr2bZnllMrQv3ff3Kql6v5plyGxISKSVe319bbMznYjZ1p3XBx+ODdrF3tvBYTzL78wjf7/84IhmSp98+JVeFRcMy1hGJeUu6pOde6gkwnF3WFZMhAHv8VxnYLKVTYt06PeQfG7dEAvOdJWwheq7psa5cciBEymm3dF7NpxB2JVmiFpB8qvr0WZWLhk72MmWn2g4alS/A4A/Af12KHTbmVbilk8bLVwWO/PEUiqZgiDUBDSKp4qZDAC8oGoTeVw5BO6aH2v3Sjyo9HR78AdWBKeA4Ch0OQrr13Ar1IJT/x78oxN0jSRPkDkdVrfInJSspRDcNXaOQvdQHLM0Vc4mbC+m/1sf2ssj0KQbhrxcW68hr6Bsq0DAT6RzmZXMWpKGUuLuwYqE11S/+UiVwuq/AcmYP4n/o7JxZucpT1mUu5lIdSnMvQbLpUuMfJgAeputFYTr0xlCk0R/w4Qb32ThesM98LLW6psKhSnx0sy00rKrZYyaoDWmiz6ULh3qRHmPAPQ++f7KeVi5Se7EglV1f9WhMn+bR2GdBgH0pvTK9xfuxSHhBF2oA+vtTyIlyZfLTsgQtoaQPXcvdPF3T9aE3MFUdp2KqyhVKVgrIgR/xyd2zmDNcJpRT0Nz/Oigs0ci/iaH6dtyBCiWuAgKHcp0+K72y5R/cnfUnkf/ZJXLeeDMFzQnpjiZedQGNuefB/Hu+PrrgU3KubflkAcwPLisXcA7vUAVCPRllOJntZO3uiA0GwiGmtNawxhP17VCrDxRmHsiWyYoYo0cV4nLeP8OQL/KMvUux5pXZY8Acuh9ysMopKz8rRtgWzU9/VY1fHT0uH/vhdIUE9QtXahcuPptus6KpPl8eu1Ot3GIwfyN5mNf/AfnNrx0=</t>
+          <t>eNrtXVuP20aW/iuEsEBijGRRFHXzYh88tjf2rhN77U42mUHQKJElsdIUqfDSbsUwsEEegsUgyBjZwSAIgonTMAwnYyQZTxBMNwZ5kNf/o+eX7DmnilRRoqRuT9uzgBUkii48rHP56tyqWH274oTBwBdOElfO3b5TrYwjF95UBLxWdpnHgkq1EnvMarXhi/bAthh3+7zVNO1ObzBo2o1+jw36TpP3bbvb61h9uz/oMafVdxqWDZe6ja5t8YEzcLputwIDxAlLUhiswsbjKNzlLgyQ8DjZdljMkYnK1oXa+Qu1xtlGrTXotq0Bfsec7YgP4OdfV+RvlXerFb4rXB44HL6FTzsicOm2YnuQBk4iwoD5cPMgTPC+Qer71UoYiaEI4DLfH1VQWg7yuwIvzq8ZRwIuSybZ54jJe/H8C/4edxLuAkssDoPs6zLJ4oSPkevbFb43BiKU5T2iga/CMVwccOSDJR68/yd4u8v8VI10593ZTX9tm42qbVnv3sHx309BY7N73YYbxPGtEG1XuRWFwRA/N6wm3C+NeRSwEcehwoDvCWApSLbx6+29yQdokhFPvBBJr1+7uTXjpg6qrLM08ep+iEq7g/wk3PEC8X6aKyMRCWqm8uS3Tz4KhkbgHR08Ghu7R4dfCCMbu56xZ8RMGP2jw98YydHht4bjHR3eFchCZnOrZrcajWajzOYWsEZvei+n8c3mMuNH4UD4/IorbVzLjFxTP1SQaswZEFVCVBnc2fG4m/rcPY9fWmavVzMb8O+WaZ6jf39hduAV56YY8Q8AOHDZ+Viw+uVw+4Intl8XgbcOO1Ea1LKB4jXwee3o8BNhnL9+BZBxcC80fACJ4xmj6VfGjjf9MyDLmT42xp6YfhMYAJv9MV7yscRbsBxOTqvtNM0NnE4AJ5cPREBivMWjWOCXDRBd+pDYC1PfrQ2Y8NeZH6CX8CgD4UkBIKkNRW28isZ96BgBeRnmjkRwBpAhwOhPv2fGk7u691nlYZq1AbeZY5dBovnSIcEyzTkUrA0GDJSwi4Ic154ZgTEOfV+AldSEHk6/nuAk/r0Auz39fvaDEwrDh4nvhYCEBGx7dPg5Gnf49Pujwy+F4U7/Ah8Tj4fG9RsXdePatY7Z5Y1WmXHtpcYd+OGtl9qkEN/DNAGDVp+Xb8lZeO1SKQfgW1bD6SZLabqrib6XHh3cT6pGEu7wIAsLctp7KcaHz0SGpgQ+fWQMczg+uYsw2nfg8oP9EDOVj3UItWqtptu1emUQam2yzkKkcNIogjzj+iz5DH03y/Vk+hnwW9rPED2i5FgpZ57Qrss6jw5/J4wRuP0EDH508DCFD5h7BsOjg+8gVXh6LzAalrEz/StGhB9WxoZWrW12+w17Y/tnsX0MGcJK48/9/kJgkEQULAq/eALmfEB5xupqpF3rNBnrllag7Zc1azxeFQo3EXOuIArJViM+6vOoWJmuwwJeui6B3KK0MZl+hZ4fMof9YK4KNSLINQALqyzerdl9u2WWJhDdjcUXLH5a1WEdb1SjOx03rcS0EOZ8xkFWMWKSsLJiXG5+6yyUwGD9dn/R/NbL2nI6SSp3sorvKqRwE8NlgWfE03tgurmS7+TVHRqw326ZZm9jwOPN31mtL9u/JbV/D/7Jy/83xy5LwJOCGvFXAzu3xYn+5hpQ1G+rd9vCvaMu3R6ziI1irZe1LZY1s2oCk4GVwFJMzsFJBoOc89WdSESSa1nNBt8g6dSQNOsinW7raKusYSTNnaDzTyIsBYZrzM1bnT5zN+Z+DuZm/+B/Xizcdqm/kBjvp9N7UHqax6k9AWRmjZvNttksRaC5geBiAnLx0tVLW5deQLipVmDwaIIEWfyguLgmDr09fcz+zihk1RrWAIrQMlBYG0ysdksVBxgOXBa9w1lUOWeZll2tSHtIfgaC+6ivmzAAsjAKXbTbQOwR48QG6Xu3gR9xxWgXK9ldG19a+NLGlw6+dPGlhy8Nk16JpkFEDaJqEFmD6BpE2CDKBpE2iNYiWkuOR7RUO+9aRGsRrUW0FtFaRGsRbZNom0TblMwSbZNom0TbJNom0TaJtkm0NtHaRGsTrS0lJVqbaG2itYnWJlqbaFtE2yLaFtG2iLYl1US0LaJtEW2LaFtE2ybaNtG2ibZNtG2ibUsdE22baNtE2ybaDtF2iLZDtB2i7RBth2g70kBE2yHaDtF2ibZLtF2i7RJtl2i7RNsl2q60LtF2ibZHtD2i7RFtj2h7RNsj2h7R9oi2J6GhsCHBYUJSgdjeOw8OBzD3ehgk3n+KGGE4yb5jOzyqrAuul/Yczl1DgtXwxUgkLyzeqUELEW8o6Ceo1bDzappr/Fu7xdvdjX87Bf+GWqixWpCq/trfD60rAbXxjAncP7P8C8NW8OSjEcXHHQDUR6nhHh1+B/A+Ovw4XQOpvmO2HWcDqWeBVBrsBOGt4F9VZJS3PS5OsJ03Yi8cKdgJ/E3gGcHQe/KQwf9CbAIrZlZBxa4NOJR9pSm3vYHKAlTm8yXIoyFVfkulSbfvnMzg9XAstXKcNqG8NrM/tgYTTxwd/JwaxBTtFfjJgS8ZOA2wM67ufpcY/fTo8HNnJQg6tWaz7ZRtM4TfNiA4pRT7zSBOx+MwAnnIt7z9zq9WJdzstLIjbVyFlCh9ga5JDqnWIwB6v8dm1OH+GkDa3By0+AaQpwVIJxz1RUDi3KC9iGXFH+gZ4LMVal8lkzHaF8cUEYDmVBB5k/sDAwZ7sUDUVEADy4YUuUtHOdLlmGyebdS6pst4SVLV3LRH12zJjcMRP8FWXMv8B2/F3dI34Kq+pkcb74aCBbLI28HdmGsQ02uavGwvzQYxp4yYhc3bzw0NWc6VL7qvQoBVazWanbK9FM1NIfacEfALs3WuOeczLqVROOb1q6AwGPA5O4wMICdJfRAyXatr2oMNZE4PMi4T/uT/4yMfJbCRTOcdH+R8JV56NbttctYrw0vv5cWLacN/vRMvnRV3ZN3O3pavnGm/zi+dZT8dY6sGLZHlO7fkfu2jw8+yzZmqqle/YJ/nAbwCOj5MCSQfByvgYUMOYjUGfFCStdqbHOSYDwgAKAIe1eHalNcdn4nRmml9Aa8x8GnOJXvx5B2PtyXPPtusdbsdXtajs1/C53XWhwSQJImYk+SVp1y8fC/sLz4fCF+u3Xkrah5nPm7FBtX7Yugla+x/PbtO+XQYpGxqr7J5q+ZarNW2y2ze2th80eZsnDgeu6KewKjBe9/nwZA88LPbXk390InqwEy0zvC/pI4rOOmDB6lx7cKNrPOQMVfP2TKc/32Y+fYTw6NFW/PajlnSIGtt3Pox3XqfgVFq0qvHPEZXgSFfvsOIXx+zNOYlcT+/ZCHsy1+OEfWv460Ndf1JrW/VrHa/2bPKrL+pEU7L+hGP09FzMv8Nuvez2b+NjaV+v2GW2L+9mf3HfOQyCFLm16DaCqMkrmjb21yWQOKGBeIu94SDRVy1Mslb6euyeT4y+lMo6hx8me3fP+mDGO2zds3sOW1mlhl5szL7PIw8ZkNOyxT45qb4AD/AsMc3/jvTb1LDoeA/9qZf47ZrBtO6uBvWNA13+qdgWJc/zkMgSwr0PUQ6LNq1XqNtuY0yWLRf7nr/2aFRBz7wsdx1CIlpVexc5WY44tkK2bHRcYnGUGtT3JVP79MdATOH99VT2rhTfx/zxg8L231wteGL8Vzlr+OiU2s2zK7VLsPFS7xkuroHdFq4OCkGoAjIFxLw9CkRjc77/r8kUbrQMSCY1W9sXYNkgUW4ADEDiDw5Ym96z1GHwOiA6EGJ0Gi3SwHR2ziKUwPEzH6VcwPmx7y62ne8EQaXVMJItn37nV/Jh4Of2ZFoaKHIkjkLDSkg9gwbHUggO1a3yUrWpTqbhzxPjAlsGntg0TBadyLMjTQwLssrKdz/tzzGx9jjo6ohnwrP4v/JHvvs4KEdHafJm2UmbW0O9VllzlmDT9GvebbyinGZLqcJdo/OV5neE/p0S1Q9B6Z1BRsGYZwIJ9bN1amZHavTt8vM1dnMwPUn5rhiXTOODl7C6wpTDWLsBHP0R+Pqsz4k38VD1ZqdFussWq/7EjZgTjTZgDF3nZu8FLjjUASJgReLgMdxYXIVZl18dPBjYMTTr4Ihnt5UAf2CgBAWkQ/55CDUSpW3po8wn76PO6Qxdx7RKUmTWcGmJ9uYif/gYCPmZ4mAt85fPv8G1G8sW7l5FRMySuDxd2CGQvkZ/bA+lc7THjNa5kXyy1tb1w0H0z860ssBqBESx56sAORe3d3pV2GBoWCYUmtI7us+K4/ts842UTC8wtF3F1D7eaKWCh1MDv2QWkpyJ6ZWa6DkgVxqHmGtSiw6kLz4IcQcYIXaUJ8jP8fQzz/DkHSeGVw9ArJEXp4YO9Nv5BkH8O19B0e9nxre9I+Bp89AD0zoGbtC6ijC6QjVsbwD/i5ZZnHMIffRhEDmYODHtDoqz7XKFdQqFuWapODEIyD0STEw339gNM0/CTAfV8ds0eEajsfkSWwZe0PBwDhy5RWq/EdA6AtI5qpFw4MqEZb3ElIq+iKeoVo3fc4qHi57ORuDdgPXBaR3WB1qKPXktoBgiNZw8IQXr8Teaqf4ehjjNvFgWJ2HLJ0iA1NZLmHq7GZXFvF6DKh2Z1BFfvdH6uyxVwKYxSCEhCLOycTTByIvDC+fGtOvR/Tbg9ErGsQyFpLpI3z8YYZZoH8sSyPw+h4JLbGDmvm3m9feyECjTdk+VmSJAmgSTQ8c8EDxGBywXqLnMvVmMkmd4ZiIo/To4CHEEvxQqq+Etg6SayhAbyaWg7v7FTf4JAfq7KdEl+9Vj8WeCIb1IIxGzBcfUCg4o88oh44UmQER3QPiAe87nrmjRQVE0x9LlaAkb+qOR5tTA+Aku5OG2VthtANYc8IUsL8rBwPNyK8v0Lc+HzJnktFKWHs4l/+AugtDvzgF8TBeZ87Yy2ae1GduRpIY/MS9AAF9uMb6syFy0e2iS8k2ekTG3tHhI2Dzr9leDnf6FyNhfYTZ/sxBTf+EPb3DTwXZ/MvCtlI1X9HWP0sfpG6lvpHPE6IGZyLmOgFWPwzmZnJum5DO/0JFkLpmUSihE0UlE7mIc15TMXEN0hkoTmA8RPv9RFu0QBgf/DRW3nRRyEWJlKgx0joo18TYC9ETaTNbEBEYAgOFjLWLyiqecCgwSZCOKod3MGQT9R1Jm4uJHvffZ+h1fDYaw9XTryaG1as3zXqzoRr46QSuCijhQEXivnd/UpCzxCAzZCzjHVkMPNnQk/deYj/NSLlcuRgdfECIfO5wxio9OSidktoPV1eal79IF0CMzTT+PmTGSt0qS6JTrO+T93oondx4URoXHRRhs4qHkeLKNh5tCpojP5Ivfwwgx4MoscuNLDuuztwjTBaZe2O0KQvzC3JjRLkoYtb3Odw6SSOOUS2m+dGns+4kHAO+lxi0eE9l9H3Zhw8K5iOZ3OmPYi65VDrDseclPoapgIsf4AI950O/QygNlBw2HmyRO1NUmjrOWfb25P4B4H7I607o8rrLEyZ8XTFoPy1cgG8c4gmzmncsSS5V/M8yBCDvR+Et0PkyD7IuclDzSUsDJPt6BrIHUk+MiOWCW1gf6E9Kj4hGsZa704RWRZ7czVw55SQOHWnoo4/W7Tia/pmk/ZR6JnJmFUVFeH2mxPsy06+SXaYekMgVFmzwxMR9deiyUodu2L7PnJ1aP9wrt66t5z3IUP4AH2FuwTTE4CeOwu7Fa6+rCTHLZAqRcNGAUPIm4Ug+5aJhAADzIEv7chvPvFZ+Iux8spoL0tZCvqTGIgFzHTQa7nXBpsfSzIwqN5mQIMiLBcYy0MmCpBi7EXMqWcwrebqdh0U73gAy2pzrTjGUYc7RD8MdQ7Zxi6kzaj8d+yHDpRlSsKP2XGqOYvoIJJCeajc7XRMdpouO9+NEN4jMtjNMLQ1UMqRSi0LlqeVFYi4TOr7rtLyoqqM3rm1fPL91Xm9eSN7UJBQjHqZJfevqzbpt2ksnjLx6lPk/rXag/IEmQxaNZ6onKeemzBjn8wjxqUypsi5ODZbPx+VTpVeMxzvkzt5PUVNQ7jwSck7UVTIxQnQFpC81CMaURCSTetGHLxM3YpDP5C2WgsC49vodm/MgVVlSyKBaqIlym+liLXOM5L7kYEryFqXTN3gSTeTI8ppMHMKlT90pqRKWJHw0xnQedf5F0QNS3g/kddxUpstEaahKtfCOiYyFffIz+q0eK3vr86m6tKlRrggtMKwLPrkS7KL5M1DrdSB6KSbvsUsLHREpTQK3TAtSaj1pzSatjpBsqEXMF3VQIoo23WdSwXzPpcJc+u0slKlLXBED7gLuJDIIDBGKdZ8rhkvROpIpNwEgoIhYnKgyky44+ZNEMdW7UwhGEcHD5kJQpgx2EFIFMBpL0S1TUiX/XsHht8bN/7haYD+7QOcQAtQuaKBYwxStsS4sFD2k7NQwyn0J231VLtBB+XkkaFEkyPsrSCU1qrQoffXJPaM6Z1tveZR2U4pMJyrpmYHLcGkC5g4Tv36U896l852z3hpOuQ/V8e/Gq09++/YZlWQnkaDkf8djIv/bANXSHlth7KKbmKlajd+WKao2N6WJ3JS0nmee9KgtHsXjG68mAoMucVo14nQ0YtGkmp9S4UpN0iEFoNsvgjMF1Y9ZFHN5O0iGYd7TZpoVgC5v7MjZQNkPNbNkNQjl3Uwu7Axfffp9XuPGOFNlXKM0XPYroJBzdkAIpRx8vSvyZ4Yh2ca7qwoYL396j8D4cxmU0QrUzCF975f3mrBuirCjXayGytzrk7vhlGIOBWeQYiacdZy2t9VS25GWNnjJheo7Exddo5z/WRBZHiwKfUKss+emhdanKG8/5sJZWudbqOIckfLK3/7rf14B7Ydz4khT7c41ewLjjTevXs2yPbOYWhfu++aVVb1ezTPlNiQkUkq8vr8235jPxWzqTuuCj2cQ7WHvbO4BoGT6xxG+P/h5RDIkT79/Sq4Ki4ZlrCMS85Z0Sc+91BNgOLusKyZDAPb4rzKwWUonz7p1Oh0gNm6JBOY7S9hc9FzTY1255ECIlNNu6byaTSHsSrJELSD5VPXpsyoXDZ3sZcpOtQ01Kl+AwR+A/7oUO2zMq3BLJ42Xrwos/JUWiqZgiDUBDSKp4qZDAC8oGoQ+UA5BO+iH2v3Sjyo9HR3+DtWBKeA4Ch0OQrr13Ar1IJT/x79exN2FpAlyh0VVq/xJyUoK0U1D1yhkL/UBS3PFXOLmXPqv9bG9LDJ9jkH427nFOvIa+s4KNMyudA6zsjkL0lBK3J1bsdCa6hd/qRI43VdgObMP8T90ds6sXOUp6zIXc6kOpbmXINl0qfEPEwBP5/WiMB16YyjS6C8FcYP7bBzP2Wc2llpdU+FQJT662eYaVtXsORTUhjTRl9KFQ71IDzngzgffP1lPKxepPV+Qyq6venamT/No7LMgwL6UXpne4v1YJLygCzUA/a0r5ES5MvlpWYKWUNKHruVunq7p+tAbmKqOUzFV5QolKwXkwBd8cvcs5gyXCeUUNA++DQpLNPJvbqi+HXegQomrgMChXKrPSq9s+Qd3av1B5H/fiZw33kxBc5d0RxOvOofG3PNg/j1bH53zKTnXtnzoAOYHl5ULOIf3qAKhnowynMx2snZ3xAYD4RBTWmtY44n6dqjVBwozD2TLZEWM0aMKcTnrn2HIF3nG3qVY89r0MWAO3Q85WOWUlZ8VI2yL5gfJqsavjh6Xj/1wskKC+oUrtQsXn023WdFUny2P3alWbjGYv5E8C+z/AHoy450=</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-1</t>
+          <t>approved 1, draft 0, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 2, rejected 0; story US-1</t>
+          <t>approved 2, draft 0, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-1</t>
+          <t>approved 1, draft 0, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-1</t>
+          <t>approved 1, draft 0, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 2, rejected 0; story US-1</t>
+          <t>approved 2, draft 0, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-1</t>
+          <t>approved 1, draft 0, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-1</t>
+          <t>approved 1, draft 0, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 2, rejected 0; story US-1</t>
+          <t>approved 2, draft 0, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 4, rejected 0; story US-2</t>
+          <t>approved 4, draft 0, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 3, rejected 0; story US-2</t>
+          <t>approved 3, draft 0, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-2</t>
+          <t>approved 1, draft 0, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 2, rejected 0; story US-2</t>
+          <t>approved 2, draft 0, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-2</t>
+          <t>approved 1, draft 0, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 2, rejected 0; story US-3</t>
+          <t>approved 2, draft 0, rejected 0; story US-3</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 2, rejected 0; story US-3</t>
+          <t>approved 2, draft 0, rejected 0; story US-3</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-3</t>
+          <t>approved 1, draft 0, rejected 0; story US-3</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-4</t>
+          <t>approved 1, draft 0, rejected 0; story US-4</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-4</t>
+          <t>approved 1, draft 0, rejected 0; story US-4</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-4</t>
+          <t>approved 1, draft 0, rejected 0; story US-4</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-5</t>
+          <t>approved 1, draft 0, rejected 0; story US-5</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-5</t>
+          <t>approved 1, draft 0, rejected 0; story US-5</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-6</t>
+          <t>approved 1, draft 0, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-6</t>
+          <t>approved 1, draft 0, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-6</t>
+          <t>approved 1, draft 0, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-6</t>
+          <t>approved 1, draft 0, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-6</t>
+          <t>approved 1, draft 0, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-7</t>
+          <t>approved 1, draft 0, rejected 0; story US-7</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-7</t>
+          <t>approved 1, draft 0, rejected 0; story US-7</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-7</t>
+          <t>approved 1, draft 0, rejected 0; story US-7</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 1, rejected 0; story US-8</t>
+          <t>approved 1, draft 0, rejected 0; story US-8</t>
         </is>
       </c>
     </row>

--- a/.qc-agent/ground-truth/test-cases.xlsx
+++ b/.qc-agent/ground-truth/test-cases.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>6f42aedbe530479ff341b9afbc3eb448972b4bf9ac5bc124edbd1842efcfc8d8</t>
+          <t>3a4218c5cc0c7c7f6e114c4c4b88d011f7b0107fc8394746f91a2be77c879cd7</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>e06f1d34178ed9cec7d4cbce16894f75b8157803617b0e2be778fe92688d4562</t>
+          <t>bd00b233b1e3078ec3e90235cd930582de992f15106acc91e7350fc05f79983c</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>eNrtXVuP20aW/iuEsEBijGRRFHXzYh88tjf2rhN77U42mUHQKJElsdIUqfDSbsUwsEEegsUgyBjZwSAIgonTMAwnYyQZTxBMNwZ5kNf/o+eX7DmnilRRoqRuT9uzgBUkii48rHP56tyqWH274oTBwBdOElfO3b5TrYwjF95UBLxWdpnHgkq1EnvMarXhi/bAthh3+7zVNO1ObzBo2o1+jw36TpP3bbvb61h9uz/oMafVdxqWDZe6ja5t8YEzcLputwIDxAlLUhiswsbjKNzlLgyQ8DjZdljMkYnK1oXa+Qu1xtlGrTXotq0Bfsec7YgP4OdfV+RvlXerFb4rXB44HL6FTzsicOm2YnuQBk4iwoD5cPMgTPC+Qer71UoYiaEI4DLfH1VQWg7yuwIvzq8ZRwIuSybZ54jJe/H8C/4edxLuAkssDoPs6zLJ4oSPkevbFb43BiKU5T2iga/CMVwccOSDJR68/yd4u8v8VI10593ZTX9tm42qbVnv3sHx309BY7N73YYbxPGtEG1XuRWFwRA/N6wm3C+NeRSwEcehwoDvCWApSLbx6+29yQdokhFPvBBJr1+7uTXjpg6qrLM08ep+iEq7g/wk3PEC8X6aKyMRCWqm8uS3Tz4KhkbgHR08Ghu7R4dfCCMbu56xZ8RMGP2jw98YydHht4bjHR3eFchCZnOrZrcajWajzOYWsEZvei+n8c3mMuNH4UD4/IorbVzLjFxTP1SQaswZEFVCVBnc2fG4m/rcPY9fWmavVzMb8O+WaZ6jf39hduAV56YY8Q8AOHDZ+Viw+uVw+4Intl8XgbcOO1Ea1LKB4jXwee3o8BNhnL9+BZBxcC80fACJ4xmj6VfGjjf9MyDLmT42xp6YfhMYAJv9MV7yscRbsBxOTqvtNM0NnE4AJ5cPREBivMWjWOCXDRBd+pDYC1PfrQ2Y8NeZH6CX8CgD4UkBIKkNRW28isZ96BgBeRnmjkRwBpAhwOhPv2fGk7u691nlYZq1AbeZY5dBovnSIcEyzTkUrA0GDJSwi4Ic154ZgTEOfV+AldSEHk6/nuAk/r0Auz39fvaDEwrDh4nvhYCEBGx7dPg5Gnf49Pujwy+F4U7/Ah8Tj4fG9RsXdePatY7Z5Y1WmXHtpcYd+OGtl9qkEN/DNAGDVp+Xb8lZeO1SKQfgW1bD6SZLabqrib6XHh3cT6pGEu7wIAsLctp7KcaHz0SGpgQ+fWQMczg+uYsw2nfg8oP9EDOVj3UItWqtptu1emUQam2yzkKkcNIogjzj+iz5DH03y/Vk+hnwW9rPED2i5FgpZ57Qrss6jw5/J4wRuP0EDH508DCFD5h7BsOjg+8gVXh6LzAalrEz/StGhB9WxoZWrW12+w17Y/tnsX0MGcJK48/9/kJgkEQULAq/eALmfEB5xupqpF3rNBnrllag7Zc1azxeFQo3EXOuIArJViM+6vOoWJmuwwJeui6B3KK0MZl+hZ4fMof9YK4KNSLINQALqyzerdl9u2WWJhDdjcUXLH5a1WEdb1SjOx03rcS0EOZ8xkFWMWKSsLJiXG5+6yyUwGD9dn/R/NbL2nI6SSp3sorvKqRwE8NlgWfE03tgurmS7+TVHRqw326ZZm9jwOPN31mtL9u/JbV/D/7Jy/83xy5LwJOCGvFXAzu3xYn+5hpQ1G+rd9vCvaMu3R6ziI1irZe1LZY1s2oCk4GVwFJMzsFJBoOc89WdSESSa1nNBt8g6dSQNOsinW7raKusYSTNnaDzTyIsBYZrzM1bnT5zN+Z+DuZm/+B/Xizcdqm/kBjvp9N7UHqax6k9AWRmjZvNttksRaC5geBiAnLx0tVLW5deQLipVmDwaIIEWfyguLgmDr09fcz+zihk1RrWAIrQMlBYG0ysdksVBxgOXBa9w1lUOWeZll2tSHtIfgaC+6ivmzAAsjAKXbTbQOwR48QG6Xu3gR9xxWgXK9ldG19a+NLGlw6+dPGlhy8Nk16JpkFEDaJqEFmD6BpE2CDKBpE2iNYiWkuOR7RUO+9aRGsRrUW0FtFaRGsRbZNom0TblMwSbZNom0TbJNom0TaJtkm0NtHaRGsTrS0lJVqbaG2itYnWJlqbaFtE2yLaFtG2iLYl1US0LaJtEW2LaFtE2ybaNtG2ibZNtG2ibUsdE22baNtE2ybaDtF2iLZDtB2i7RBth2g70kBE2yHaDtF2ibZLtF2i7RJtl2i7RNsl2q60LtF2ibZHtD2i7RFtj2h7RNsj2h7R9oi2J6GhsCHBYUJSgdjeOw8OBzD3ehgk3n+KGGE4yb5jOzyqrAuul/Yczl1DgtXwxUgkLyzeqUELEW8o6Ceo1bDzappr/Fu7xdvdjX87Bf+GWqixWpCq/trfD60rAbXxjAncP7P8C8NW8OSjEcXHHQDUR6nhHh1+B/A+Ovw4XQOpvmO2HWcDqWeBVBrsBOGt4F9VZJS3PS5OsJ03Yi8cKdgJ/E3gGcHQe/KQwf9CbAIrZlZBxa4NOJR9pSm3vYHKAlTm8yXIoyFVfkulSbfvnMzg9XAstXKcNqG8NrM/tgYTTxwd/JwaxBTtFfjJgS8ZOA2wM67ufpcY/fTo8HNnJQg6tWaz7ZRtM4TfNiA4pRT7zSBOx+MwAnnIt7z9zq9WJdzstLIjbVyFlCh9ga5JDqnWIwB6v8dm1OH+GkDa3By0+AaQpwVIJxz1RUDi3KC9iGXFH+gZ4LMVal8lkzHaF8cUEYDmVBB5k/sDAwZ7sUDUVEADy4YUuUtHOdLlmGyebdS6pst4SVLV3LRH12zJjcMRP8FWXMv8B2/F3dI34Kq+pkcb74aCBbLI28HdmGsQ02uavGwvzQYxp4yYhc3bzw0NWc6VL7qvQoBVazWanbK9FM1NIfacEfALs3WuOeczLqVROOb1q6AwGPA5O4wMICdJfRAyXatr2oMNZE4PMi4T/uT/4yMfJbCRTOcdH+R8JV56NbttctYrw0vv5cWLacN/vRMvnRV3ZN3O3pavnGm/zi+dZT8dY6sGLZHlO7fkfu2jw8+yzZmqqle/YJ/nAbwCOj5MCSQfByvgYUMOYjUGfFCStdqbHOSYDwgAKAIe1eHalNcdn4nRmml9Aa8x8GnOJXvx5B2PtyXPPtusdbsdXtajs1/C53XWhwSQJImYk+SVp1y8fC/sLz4fCF+u3Xkrah5nPm7FBtX7Yugla+x/PbtO+XQYpGxqr7J5q+ZarNW2y2ze2th80eZsnDgeu6KewKjBe9/nwZA88LPbXk390InqwEy0zvC/pI4rOOmDB6lx7cKNrPOQMVfP2TKc/32Y+fYTw6NFW/PajlnSIGtt3Pox3XqfgVFq0qvHPEZXgSFfvsOIXx+zNOYlcT+/ZCHsy1+OEfWv460Ndf1JrW/VrHa/2bPKrL+pEU7L+hGP09FzMv8Nuvez2b+NjaV+v2GW2L+9mf3HfOQyCFLm16DaCqMkrmjb21yWQOKGBeIu94SDRVy1Mslb6euyeT4y+lMo6hx8me3fP+mDGO2zds3sOW1mlhl5szL7PIw8ZkNOyxT45qb4AD/AsMc3/jvTb1LDoeA/9qZf47ZrBtO6uBvWNA13+qdgWJc/zkMgSwr0PUQ6LNq1XqNtuY0yWLRf7nr/2aFRBz7wsdx1CIlpVexc5WY44tkK2bHRcYnGUGtT3JVP79MdATOH99VT2rhTfx/zxg8L231wteGL8Vzlr+OiU2s2zK7VLsPFS7xkuroHdFq4OCkGoAjIFxLw9CkRjc77/r8kUbrQMSCY1W9sXYNkgUW4ADEDiDw5Ym96z1GHwOiA6EGJ0Gi3SwHR2ziKUwPEzH6VcwPmx7y62ne8EQaXVMJItn37nV/Jh4Of2ZFoaKHIkjkLDSkg9gwbHUggO1a3yUrWpTqbhzxPjAlsGntg0TBadyLMjTQwLssrKdz/tzzGx9jjo6ohnwrP4v/JHvvs4KEdHafJm2UmbW0O9VllzlmDT9GvebbyinGZLqcJdo/OV5neE/p0S1Q9B6Z1BRsGYZwIJ9bN1amZHavTt8vM1dnMwPUn5rhiXTOODl7C6wpTDWLsBHP0R+Pqsz4k38VD1ZqdFussWq/7EjZgTjTZgDF3nZu8FLjjUASJgReLgMdxYXIVZl18dPBjYMTTr4Ihnt5UAf2CgBAWkQ/55CDUSpW3po8wn76PO6Qxdx7RKUmTWcGmJ9uYif/gYCPmZ4mAt85fPv8G1G8sW7l5FRMySuDxd2CGQvkZ/bA+lc7THjNa5kXyy1tb1w0H0z860ssBqBESx56sAORe3d3pV2GBoWCYUmtI7us+K4/ts842UTC8wtF3F1D7eaKWCh1MDv2QWkpyJ6ZWa6DkgVxqHmGtSiw6kLz4IcQcYIXaUJ8jP8fQzz/DkHSeGVw9ArJEXp4YO9Nv5BkH8O19B0e9nxre9I+Bp89AD0zoGbtC6ijC6QjVsbwD/i5ZZnHMIffRhEDmYODHtDoqz7XKFdQqFuWapODEIyD0STEw339gNM0/CTAfV8ds0eEajsfkSWwZe0PBwDhy5RWq/EdA6AtI5qpFw4MqEZb3ElIq+iKeoVo3fc4qHi57ORuDdgPXBaR3WB1qKPXktoBgiNZw8IQXr8Teaqf4ehjjNvFgWJ2HLJ0iA1NZLmHq7GZXFvF6DKh2Z1BFfvdH6uyxVwKYxSCEhCLOycTTByIvDC+fGtOvR/Tbg9ErGsQyFpLpI3z8YYZZoH8sSyPw+h4JLbGDmvm3m9feyECjTdk+VmSJAmgSTQ8c8EDxGBywXqLnMvVmMkmd4ZiIo/To4CHEEvxQqq+Etg6SayhAbyaWg7v7FTf4JAfq7KdEl+9Vj8WeCIb1IIxGzBcfUCg4o88oh44UmQER3QPiAe87nrmjRQVE0x9LlaAkb+qOR5tTA+Aku5OG2VthtANYc8IUsL8rBwPNyK8v0Lc+HzJnktFKWHs4l/+AugtDvzgF8TBeZ87Yy2ae1GduRpIY/MS9AAF9uMb6syFy0e2iS8k2ekTG3tHhI2Dzr9leDnf6FyNhfYTZ/sxBTf+EPb3DTwXZ/MvCtlI1X9HWP0sfpG6lvpHPE6IGZyLmOgFWPwzmZnJum5DO/0JFkLpmUSihE0UlE7mIc15TMXEN0hkoTmA8RPv9RFu0QBgf/DRW3nRRyEWJlKgx0joo18TYC9ETaTNbEBEYAgOFjLWLyiqecCgwSZCOKod3MGQT9R1Jm4uJHvffZ+h1fDYaw9XTryaG1as3zXqzoRr46QSuCijhQEXivnd/UpCzxCAzZCzjHVkMPNnQk/deYj/NSLlcuRgdfECIfO5wxio9OSidktoPV1eal79IF0CMzTT+PmTGSt0qS6JTrO+T93oondx4URoXHRRhs4qHkeLKNh5tCpojP5Ivfwwgx4MoscuNLDuuztwjTBaZe2O0KQvzC3JjRLkoYtb3Odw6SSOOUS2m+dGns+4kHAO+lxi0eE9l9H3Zhw8K5iOZ3OmPYi65VDrDseclPoapgIsf4AI950O/QygNlBw2HmyRO1NUmjrOWfb25P4B4H7I607o8rrLEyZ8XTFoPy1cgG8c4gmzmncsSS5V/M8yBCDvR+Et0PkyD7IuclDzSUsDJPt6BrIHUk+MiOWCW1gf6E9Kj4hGsZa704RWRZ7czVw55SQOHWnoo4/W7Tia/pmk/ZR6JnJmFUVFeH2mxPsy06+SXaYekMgVFmzwxMR9deiyUodu2L7PnJ1aP9wrt66t5z3IUP4AH2FuwTTE4CeOwu7Fa6+rCTHLZAqRcNGAUPIm4Ug+5aJhAADzIEv7chvPvFZ+Iux8spoL0tZCvqTGIgFzHTQa7nXBpsfSzIwqN5mQIMiLBcYy0MmCpBi7EXMqWcwrebqdh0U73gAy2pzrTjGUYc7RD8MdQ7Zxi6kzaj8d+yHDpRlSsKP2XGqOYvoIJJCeajc7XRMdpouO9+NEN4jMtjNMLQ1UMqRSi0LlqeVFYi4TOr7rtLyoqqM3rm1fPL91Xm9eSN7UJBQjHqZJfevqzbpt2ksnjLx6lPk/rXag/IEmQxaNZ6onKeemzBjn8wjxqUypsi5ODZbPx+VTpVeMxzvkzt5PUVNQ7jwSck7UVTIxQnQFpC81CMaURCSTetGHLxM3YpDP5C2WgsC49vodm/MgVVlSyKBaqIlym+liLXOM5L7kYEryFqXTN3gSTeTI8ppMHMKlT90pqRKWJHw0xnQedf5F0QNS3g/kddxUpstEaahKtfCOiYyFffIz+q0eK3vr86m6tKlRrggtMKwLPrkS7KL5M1DrdSB6KSbvsUsLHREpTQK3TAtSaj1pzSatjpBsqEXMF3VQIoo23WdSwXzPpcJc+u0slKlLXBED7gLuJDIIDBGKdZ8rhkvROpIpNwEgoIhYnKgyky44+ZNEMdW7UwhGEcHD5kJQpgx2EFIFMBpL0S1TUiX/XsHht8bN/7haYD+7QOcQAtQuaKBYwxStsS4sFD2k7NQwyn0J231VLtBB+XkkaFEkyPsrSCU1qrQoffXJPaM6Z1tveZR2U4pMJyrpmYHLcGkC5g4Tv36U896l852z3hpOuQ/V8e/Gq09++/YZlWQnkaDkf8djIv/bANXSHlth7KKbmKlajd+WKao2N6WJ3JS0nmee9KgtHsXjG68mAoMucVo14nQ0YtGkmp9S4UpN0iEFoNsvgjMF1Y9ZFHN5O0iGYd7TZpoVgC5v7MjZQNkPNbNkNQjl3Uwu7Axfffp9XuPGOFNlXKM0XPYroJBzdkAIpRx8vSvyZ4Yh2ca7qwoYL396j8D4cxmU0QrUzCF975f3mrBuirCjXayGytzrk7vhlGIOBWeQYiacdZy2t9VS25GWNnjJheo7Exddo5z/WRBZHiwKfUKss+emhdanKG8/5sJZWudbqOIckfLK3/7rf14B7Ydz4khT7c41ewLjjTevXs2yPbOYWhfu++aVVb1ezTPlNiQkUkq8vr8235jPxWzqTuuCj2cQ7WHvbO4BoGT6xxG+P/h5RDIkT79/Sq4Ki4ZlrCMS85Z0Sc+91BNgOLusKyZDAPb4rzKwWUonz7p1Oh0gNm6JBOY7S9hc9FzTY1255ECIlNNu6byaTSHsSrJELSD5VPXpsyoXDZ3sZcpOtQ01Kl+AwR+A/7oUO2zMq3BLJ42Xrwos/JUWiqZgiDUBDSKp4qZDAC8oGoQ+UA5BO+iH2v3Sjyo9HR3+DtWBKeA4Ch0OQrr13Ar1IJT/x79exN2FpAlyh0VVq/xJyUoK0U1D1yhkL/UBS3PFXOLmXPqv9bG9LDJ9jkH427nFOvIa+s4KNMyudA6zsjkL0lBK3J1bsdCa6hd/qRI43VdgObMP8T90ds6sXOUp6zIXc6kOpbmXINl0qfEPEwBP5/WiMB16YyjS6C8FcYP7bBzP2Wc2llpdU+FQJT662eYaVtXsORTUhjTRl9KFQ71IDzngzgffP1lPKxepPV+Qyq6venamT/No7LMgwL6UXpne4v1YJLygCzUA/a0r5ES5MvlpWYKWUNKHruVunq7p+tAbmKqOUzFV5QolKwXkwBd8cvcs5gyXCeUUNA++DQpLNPJvbqi+HXegQomrgMChXKrPSq9s+Qd3av1B5H/fiZw33kxBc5d0RxOvOofG3PNg/j1bH53zKTnXtnzoAOYHl5ULOIf3qAKhnowynMx2snZ3xAYD4RBTWmtY44n6dqjVBwozD2TLZEWM0aMKcTnrn2HIF3nG3qVY89r0MWAO3Q85WOWUlZ8VI2yL5gfJqsavjh6Xj/1wskKC+oUrtQsXn023WdFUny2P3alWbjGYv5E8C+z/AHoy450=</t>
+          <t>eNrtXeuP29aV/1cIYYEkqGTxJVLKoh9c2xtn68Ree5xNUgTGFXklMUORMkWOZ2IY2CIfgkVQtEa3KIKgaBzDMJzWSNK0KDqDIh/k9f8x+5fsOedevjTUazyyPeNxAo0ePOS99/c7j3vu63bNCYOe7znxuPbm7Tv12ihy4U3Ng9faFhuwoFavjQdMb1nwhcFMXWs7LcdRHduxexbXNNOB/7rttqtqWs/uqppq95y20TFt0+p1NKZ3uW07bbvjuHYNHjCOWZzAw2puxHox3D3m4/iGw8YcS1DbONc4e66hndEarV7b0nv4HXNuRLwHP/+iJn6rfVSv8S3P5YHD4Vv4tOkFWGI28m70ksCJvTBgPtw8CGO8b5D4fr0WRl7fC+Ay3x/WsKocKu96eHF2zSjy4LJ4J/0cMXEvnn3BP+ZOzF0oEhuHQfp1Vi02GkXhFnex3WI+wlLfrvHtEQhhXT4mGfgqHMHFAcdysHgA7/8F3m4xP5FPuvNRftNfmKpWN3X9ozv4/JsJtFh+r9twg/H4VojA1W5FYdDHz5puwP2SMY8CNuT4qDDg2x4UKYhv4Nc3tnc+QTyGPB6EKHrl8rWNvDRNaMomS+JB0w+x0e5geWLuDALvZpI1RuzF2DK1J7958mnQV4LB/u7jkbK1v/elp6TPbqbFU8bMU7r7e58r8f7enxRnsL9318Mi5Jg7lsFbnWOHeUrlxYDzmwXAz4SbOeY95o/5nXoVMc7IB2XX6qq6dnp88sm66IE0iAeTv8I3sRcom/JttL97H6nzS2U08CbfBArw4/5I8ff3PiuTpNdrtbm9OkkA+DhiTvzSUSTDEXCtwPFIILgQuKPQC2Llyd0iFqCJvw3gdfeep2xNvoKmBxSo6X/rwaWTXbhU4PDkLl4qcLqHfweTeyXt1Rt6R9e5UQWMDsWmN53jqsZlXVONGbomtWnsDLib+LyxTYUNe57P33bLataQ39fwRiPO4D61EFuFShTFZ/ELXe10GqoG/2+o6pv0/09UG17RcXpD/gncDy47O/ZY82J449zAu/GOFwwWaW6UBI20jOMFzHlrf+9XnnL2yttEkxAV8nNnkKqtM/kh1dcys+YZer1htjTN0I4vVdbn5WdSa4pGjWV4JCF2X3IuDcHyHORTbv8Fp4LZdHJalmOop3RagU4u73kBVeM9Ho09/FKrZ/ZrECa+2+gxz18EP1Av5lFKwlUJIKQVKa28juA+cpSALAlzh17wBjDDA9CffsdWsjAutyzHPJnOaA4flosVD7AiQ/itC9MAYzS4PKw3EwogIEoAcJ7FRxiNHjdZNYLGK6fLgOKqUSFEut4WVmRZ6FIBZRT6vgcoSfj6k6930Az/3gPcnn6X/+CEnuKD6R6EoMsxRYhfILj9p9/t7/3BU9zJPyhQ5KFy5er5Irhmw7JMo1dpsc2Z4Pb88NZLHbwfInAPkxgAqr/U2n2NJaniboN6P4jrSp9Y41O/Abnz5C5ift8Bld69H2I37rO52m02bLXNtdYxIcDLotMrE2bl8GAOVagEEB4sJgt67CnCxOEmD1IvIJgxSGQ/M80AwKdPJbNmcKpIoVbD0LSe41ZRqPXKevaZWSAniSLoLVzJk0Gh78pUkNmysCX4rcKvEAJG8VIZoCy/tCgJtL/3O08ZguePAfL93UcJfMBMYdDf3/0W4v2n9wJF05XNyT/RbHw/14C0Gi3DbeudY4f+C8gPz4QeP4lM4DHD3lLbXc08xf4w2I+hizcX/KnfnwsN4ohixdIvAw8sfpqcnMcHq6E7juawKj5YJyXhOAfjQygvhX3N2+kAwJ0cQXHdjRGL2JBG5OYMEgDcc/G+ysc8LoN6M5ncS5V+GlPRVeh7xIgBppmxT7H7MMHUdFhG3DYYa/eOHeLrTPQsNwQEN/GmjH8UElpDPuwCpqVhoaV4tEDrNyjTE0++wkgvpPRAeYRQiaBzCdo/X8cd0+rp2onS8dWiPe3woI/Dkk03jwnodqPd0ttquwp0++QYdtWcg2IZpxIyZzfOXVxg1+eac5+N4xuUZL3Bt9lw5PNFBv0ioKpgiURuVnESstsOOe8ndxmOFpaTQfPgbTfUlsv0yiRA+2TAOxPWwoDL2wHZ5OaH+HGVwZYm3qRBd1ku7prseuRe/0Cx1acBdbk/V8aIW98Dx1xK2xbGX+ajaHbNlnr8UHxBvviohtqWRv+tQkaFeJCWIB/K9eYPv82GXz+jNVRA3+oehF9/VSdqrZJUW2347NL+7oMdxWXBQBlP7gF0U+Nnqw+VIYCW3rXa7NgBuOYRsjkqnI+d4qfts9Angju/Ewbx4D+9MT5sJ/2ObVJ0tcNZhE/SzTvZIOvRjqyKgCslgoi1YtRjnLDz7VxPjBxgXVO37BPFgRUDraMBNRm5DMrboI/4nC1PDK536F8J8usLEG/elu9ueG5FJJf/WD2xqOG5i+K561TaKdakZV4wXxNZ07Vaqto5Nf2HMBtwScUUDORIxiWJToYHzpSurZNBjcNTaMoRrcwkV9cNjZ8y6ciYpK3Vz1TCvYK74S27y9xTuNcAN3vB/54v3bZojDgWeWVNV5cZQSICdpnZMk54vLPmWOcEEezomKU2WkbHsFuV1FJPeCydwXL+wqULGxfWH97Wa/DsaIcSpdOh9nzc35/8wA4drqgN11KdHj/pIL94gFcAMR54+7s/JvCXDZUxYJYDuj2556STyBcAy1XDUo3jB+xzDk3WSYTGSqq+DEWerXeiN1S11WOVKU79lYsWkmCcjEZhBM/9N4/7UNU4Snj90FEE9AMoqT1k2UqWtTt4TIR/HgyUoD948ojBnxAHKkUpFlBB03u2wY4dFV6GnkvNgQIHLos+yGhQrwkwRXl6gk+1a/AALMIwdBHBnrdNBadiUHtvafgRF3Js4QSGLRzQ3mrhC05k3LLxpY0vHXzRVHolGY2ENJLSSEwjOY0ENZLUSFQjWZ1kdfE8kqUpE1s6yeokq5OsTrI6yeoka5CsQbKGKCzJ0vj7lkGyBskaJGuQrEGyJsmaJGuSrClqSrImyZoka5KsSbImybZItkWyLZJtkWxLNBPJ0ozPrRbJtki2RbIWyVoka5GsRbIWyVqijUnWIlmLZC2StUnWJlmbZG2StUnWJllbAESyNsnaJNsm2TbJtkm2TbJtkm2TbJtk2wJdkm2TbIdkOyTbIdkOyXZItkOyHZLtkGxHUENyQ5BDhW4fcnuxFVvU/76w7XDuKoKsiu8Nvfi5dYnlQ0tdl9J8KqjuAvtmWKZltE9d3WodY6xxgzWCJJ2lUXBueMXzc23Bk0+HFNFs4hB/orj7e98CC/f3PksWIG+1+IxhwFPPtppnK7PhKIyKnCOiIJeUNXKp0qocnlJdR7Uc55RSh4uzN4PwViBjbHnbZXkiQ9nnzZRDx9Vmw+au06scETBPvt9ZDZ9mOBKVWGayiMRJilQkSbr7u9/GSjfZ3/vCWYBRj/OWbRw7jF6QOk/3ZkYMV2K8Jzsxt++sEXRxbYo9zgpKcadC0STNvzuHIYHd0FTOdbOKBPYrFyA64bDrBVSUq7T9RVUvFtqo8CneGSFOeGsvAsv80eEzJ2Pu9xpw90aUHLWNP5dXTMG7i4EP4osjmTSfJYZhOVW7t73kLDlWaZLrU5m49z/4cF7ShB1VD7fwXGlPjp6Ac4IM8ch8kvLvadry/QWENLnaa/FTQh4VIZc1fUCfjfBZ7d8iRl4DS6jAw54vEZ1nNZKO5XCTn7pS2nE0cPzEpca4fmCE4Re17Rre5dCzMvM7Noija3CZGxFte5Jvj1IwTTHuu6jIKjb5Nv2dQw7jjNaw9TZrVSTijBOwzSFSY+HI4jPuNZbteFjaauzINjxEiNqqy7izOkSv6CLUwgZ2uCBxhY3rdPUFb1y3UeSQnCQ0oE2O+h4LRKJ9E/cuW6DUHUPlVRsXnDLmiBlzYKvDtbEhy6ikq6oWMaCnW61jx4Aj8vlHvBfqywKqY7RaLjsF9TCgqifDtuuNlmbYaqVmnw52rNe2/0RtvWlMMeZCEoUj3rwEDQYPXDNdUiuxSlKCKNPp9ix+7CjzcjqDnwiXUGLB9Y1za8a+sKheop/tW7c0DSxLNTTtlAZHRIODxoDcx89Df5PFbG18wMJNG4Tig4sr6jOOAB12H4zSucnpuExhTyQ3LKzuFvsk5l3YMo3aels1e6cO6OgckMs8f+dl3Ei9whCJQmdzNLDkC8xOu6tpnVOzs9jsZDR4mc5lmEmBny7GvtMwLZWzThX2nVfXVuCaJrWz8mqH8rYst9O31YsdCr9Or3bITg1ZcuFL+SSOYmZT+pEsINnfewivYBl+mZCB+CxYQI9Wx+rZ3WNHj7UvYXs2qNeA9IE9FEeDyT9EpJEjap7RGrrW472KXLV5mnlcfvAh4FETrk140/GZN1w0iQKvUfBouxlbLIk7LrfTEmLo6Lre7Rw7DFfSytXPwDpCXOR3eBKZu7/3oHwsWWkgqPJ0MvOM0TA6rs3aVRgZr/w8xsRrDDjzccNgaBnf6w/iBVBdSa/LMrLFyceF3WHnao7RaLdtXjVz0XwFzxJZHBqnQ8jZTAux4OrjsHvw9Cn4srZG2EVgCw9ZxvkVMW81tK6pWZWYt16B7o3DRrEzYAe6N/L7MpyroCnNbehETeoPLYDyZzSzVGrq5XNXc0SbWRFX2nESoXV11rLMYwfti1LnAhVC323Ae9/nQZ/Cz8Or9dEQIStcMyuW4vzvo7QLs7Lmt2gzKctRK9LqrdNYd8mYqssAlIYIqcZ8jF4AuzviHfZ2miOWjHlFnye75EDvVvyyRJfnCt5akdevjn7PUV3LPXboH2XfdZ2IrgPQQpQtDhqr6sW28IhZq2t09CpsT1PcR8WDiI+T4ZpU+yrd+7C6rTdc0zKrDvpsnaSU9Rp0e1lM1wLpUtpt4dyobldTK7TbOvXbSx7RFgQJ8xsRx7nOuMVxtmWOy2I25jh0scUHnoPDC6Wp0guSkHyodCf3QsXBl3yX6VW3C0eQmanZrnbsQD6qjbNWAU3uLeCJRb20kUBtJaTS2UzpMj9aPl5YyT0PKbOhdhyLqVVInS73XIc6jlif06oWfHPN+wQ/wGOXV9MPJt8kikMdLDCxX+NmrHi0Q3knQ1VV3Mlfgn5T/HhgAEF2vIrbhhRpYTVszdS6rSpaWMd+YYL6LAA34Zbhwn5wti5BXF3Q1iNbm4AodTRLrzaz1qs9wPvs+C7S4zEtdXuzdi0c8nTZ29I6fEGwQqw94q44E43uCJq990CekloIqYoJcZym+uVoaqi3yAu7Yai9Xs+q4oV9Mg574DfnHfZgqp0panTWQgeX91jix4dAnvl+NtgBDdnzouFZ3/8pbrKXThODQk+Bqqlt/fiBumZl7zwPZT9KeKdGI8l2NK9uXIbOFYtwVcJ0R6qwr2mREJ2Gq2uWVUmIzqn1PzJC5PjV3uwxf8zr8x3Cu2FwQXawCdv3P/hQnMB4aO9QYAsFdakHKDAFql3mRo/ZvCo/ah3fuT2reQBzih7m86JE7hRmMeLDDz98nnSwoT+utU3brZg1bJ+c/vih8cXpXgOAJwRwF2TBkkC5KK6smOgjTkuc3du2xXpvg7WOHQ4vxzFqR4IbovLfEqttPqwr4tDNtEe82sFqNh5RbzsGN6ogffWGqaFvvTyc+YwRKb/gDKK3lYt0+dQcreLkLZmWBmhdj/WDcBx7zrgIl91Qbd3umlVw2acauFADE9dblPrAMyjpupKqQei7g1mrx6P6YY+hRPQMs92ytWOH3pr82EporO6w2mf0hmPYLVZxZGD7FRyLXcm6QcHcnWWzhHixF/DxePZU1PH+7t8CZTz5KugXETIars2ZpVUhZLx6KrHMHj7n85NVu8zZTEYKSSk7eWL9ZrIDCBStVmk4E4oDjQf8gnAcCyRODgEMau9NHtOkYtwcFfNyQ0AvKd65mMjDLN/3uBBw90ehgO+dvXj2XXg4SyeNv455AUoO4u/ABeo/vKEMJ19lY7AiVUibUtFiIRS/uLFxRXEwC0FHdDtgWsnyjgYiuyi2gKQptcUCBf2EstNiS9cz0LZUMwMrhleUVrvSJK8due7EwRyFH1JWW2zdVshjYs0DMRo1xNEKKqIDHSY/hBgLikITAr6gdPji9vlXzJJ/vaP4cPUQxGJxORi4yTfi1Fz49oGDT32QKIPJn4NB0fYNQIMGypYn2ihCQ9hXuuIO+LsoMhuPOfS5CpXAwsGDfyis/c0aqFUelinUFIKWCAR9ahjwb98zsrK/CjAtRKkgeVyzM2BUo6x4fY8BOGIZD3DvMQj6HvQg62XgoSnRKtyLqVHR2vPUqBShz4pq4QHv6TNo+8CmB91KzDwXWDoQI4dBH9FwcIBiUIG33IB0MY1xWDLo16cpi2zF4y7FjPxicdMry3xdgqrtnKpY3vtD3PT0fqi8FoARhUoIKqJOxoPig8gJwsuvlcnXQ/rt4fC1AsXSIsSTx7jzcc5ZkP9BZOjAlw6o0oI72DL/fu3yuylpCirbxcRgLAkaR5NdBxzAeATWtZj+z+rUyesk2gyfiTxK9ncfQeyEHyrbK6b9LMg0lKiXV8vBTWNlaXATZ2yzv8fF+r0+YOOBF/SbQRgNme99Qnb+jdJ6CjKlORHRPCAf8L6j3BwdbIBo8rfKRpA1N4qGp6BTPShJeqcCZ2+F0SZwzQkT4P6WeBi0jPj6HH3r8z5zsq67oPUAdfmP2HZh6JdVEMyT50yBPUvzRHtmMFKNwU7cC5DQewvQzx+RVd0sm5R0LVmkbO/vPYZi/jNdLuaCW4pZF2l2PzdQk7/Q4pVfe4T5H0p7nUh9Rax/FDZI3kp+Iw6RwBbMq5i1SYB+cUqTM2xw/zvRENRcuRcCDj5yZCGyKk5ZTVmIy7jAfgBKTYOkD+LCXCOk8e7fR9KaHqzkwRrJqo5RFhfh39tRtkO0RAXN9kgIgEBHIXztwcYq1bfvYYwmDFVG76DPduR3VNusmmhxf56z1/HZcARXT77aUfRO01CbhiYn22DQ8WlA8R42JG5/6O+U6lkBSM6MWWXHIgYDMVgo7j0DvwJIWb2yati473QiRqSzotKhAXHxgIqmbHnxizABVLC8xSG4SptbRkkjDHgfkPV6JIzc6GBtXDRQxM26cuXqeZw/DkWBGwg7kk1V6kGwB15iiytp6FvPzWMaw5G3qXLzB+qNHuW8N2Zdn8Ot4yTi6NXGpB/gWx7Hko4B344VmiJPaaMHYiZGUIKP6uRO/uZNxfayzfDZ0zVeAiooxfdwQTHmQ7tDLA1kPUw82C4zpthocpRRDDGJKURQ+j5vOqHLmy6PmecXGwbxK7gLsI3QRyiFbxXBpfT/aYQA4t0ovAVtPsuCLPIclPQuhAGi+MUIZBtqvaNELKu4jh2F4vE4Q5KRRcvMaUzzYp7cTU05xSTO5B/wUB9tdBHH4eSvVNtfU45QaFa5qtncDQGRaF9ZdxF6QCBXmrIjFiQGlHeUzVEEtutDV6XRDber0TWLcY9HfRe5my1x7gA0VMBfOZK75y+/IxUij2RKnvAggApL4nAotsUtcAAI8zAN+zKMc6uV7YgyHaxmFbEKLl9IYycBYx0EDVeUYJJvZmRGHWcRkCDJyx2MWaQTHZKy70bOyWAx7wPi7QaYpMIbQESbldouuzKMObphuJnO/imFztj6ycgPGU77oAZ25AL+gqGYPIYaCEslp/cJg+mi4f0sLgIiou2UUzMdlXCplJKTcWp1JzGrExq+KzTBTPaO3r184/zZjbPFZJ0om1RCb8jDJG5uXLrWNFVzpsKIq4ep/Sv0HSh+IGVIvXHe9FTLKZXBqVP3hshPCaWMujglFL8YVatKp+yPN8mc3UywpaC789gTOtGUwcQQ2RVQe8mHoE+JvXinWbbhs6obMYhnsvxJqcI4++5bNmVB6qJLIZxqqU+UYVas1izDSOZLPEzWvEXh9FUeRzviyeKatDrES5/ygqJJWBzz4QjDeWzzL8sWMF1H3cSlW8U6URgqQy28Yyx8YVfOEc9v9YPEu6hP9ZlJjeqGKDiGRc4nawSzDH9K6mI/EK0UE/fYogHWiBpNELeqFUSti0FrqrRFhqSPOsj5chtUVKWg7nmtQN+zWmEs/X7qyuQlrjcG3gXciYUT6CMVmz6XBa5k61CE3ESAgDxiWVFFJF0y8qt4MZnEkwzGKoKFzSpBkTLg4IkmgKexBM0yBVXoLSi7cO0/LpWKn15QLCE4qC1ogXIfpozGIrdQtpAiU8Mo9iVud2V3QW4HntXBLuZXUEq0qGxFYatXt4zihK5SyqMym1IudCyDnpxciksKmBlM/PpxVna0+E9+k+bWUOV+qWwnVP7Xn/zm/TdkkB1HHgX/mwMmQ1oIx+uVObbSs8tmIm9q+XxLhKgF3RQQuQm1ehZ50i5peP6ir7wee+h0qaR1ZZwMhyzaqWcHVLmiJWlSPLTtl8EbpaYfsQg0gW4HwTDoPU2nnkPo6sSO0AaKfiiZJXqD0L3L64WZ4UtPv8v6uGPUVOHXKAwX+QroyDmbUAnZOPh618sOGYBgG+8ue8B4+dN7RMYfq6iMKFAyh9r7fnWuCftNEQ4olHtDVeb1yd1wQj6HnDPUIq+cvkzaW2/JCekzE7xkQssLiqZNo9D/1InMdhalPCH2s6fUopCnqE4/ZpXTC5lvT3bOkSmv/d9//c9r0PrhVHUEVFtTyZ5Aeff6pUtptKeWQ+vSfa+/PS/XW7BMGYbERAqJF+fXphPzWTWNotE65+P6kW3MnU3tJhVP/jzE97s/DqkO8dPvnpKpwk7DrKIjE7OUdEXOvdISoDu7WGyYlAGY47/EALNk5LKYu006JGKs3PJi0Hfcf7HsPRfkWOcOORAjhdrN1KtchTAryWI5fudTr6+oVVnV0MhepOi0eF79VmqqH4L9ujB22IjX4ZZOMp49KhD0yfl4mAIkjpA3BSAWODTwpLI0NhG81NByBcLUGX+U7hd2VLbT/t7vsDkwBBxFocOhkm4zQ6EZhOJvj4F5dQ8ETRA7HGxqGT/JulKDlPeBgWsks2fagJmxYlZjYyr8L+SxB6ln+gKd8J+mBuvIahRnEiEwW8I45N3m1ElDV+Lu1IhFIal+/mcygCvaCloJAv4/dDbfmDvKU5VlLsdSNoW5FyDYdCnxDwrwDV4ThUl/MIJOGnNiypD5bDSewid/lhxdk+5QBj5F2KYSVvV0twdsjTg7KUX0F2nhOc708f3VclpZlazpDqnI+sodKrqkRyOfBQHmpYo901u8O/ZiXmoL+QC8BaYRU1MmPs0K0GIK+tC03M3CtWJ7FBOYsh8nfaqMFSpGCsiAH7DJ7TMYM1wklpPT3P1TUBqiGYqjoEXejjvQQxnXgYF9MQ6fdr3S4R+cIfpHYZC+oIQW/Io3k9TcEvvSouLVp9iYWR6Mv/Px0SmbkpXaFGuFQT+46LmAcfiYeiBivF0AJ6KdNN0dsV7Pc6hQhdRwoUyUt8NWfSg581CkTOb4mKJXoVLm+TN0+V4WsbfJ17w1+QE4h+aHDKw0ytLOekNMi0Z8yxunTTvFHpeP/HBnTg2a595unDt/uLZNO03NfHjsTr12i4H+RuKIyf8HBoPe8w==</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>6f42aedbe530479ff341b9afbc3eb448972b4bf9ac5bc124edbd1842efcfc8d8</t>
+          <t>3a4218c5cc0c7c7f6e114c4c4b88d011f7b0107fc8394746f91a2be77c879cd7</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.2-451131</t>
+          <t>TC-AC-1.1-c63e59</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AC-1.2, AC-1.9</t>
+          <t>AC-1.1</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Gọi API tạo lịch mà không có phiên hợp lệ nhận từ chối</t>
+          <t>Đăng nhập sai thông tin không trả về phiên hợp lệ</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -1011,14 +1011,14 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>POST /api/run-schedules -&gt; 401,403</t>
+          <t>POST /api/auth/login -&gt; 401,422</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.2-c56c30</t>
+          <t>TC-AC-1.1-ff58e7</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>AC-1.2, AC-1.9</t>
+          <t>AC-1.1</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Gọi API tạo filter profile (chức năng admin) khi chưa đăng nhập bị từ chối</t>
+          <t>Endpoint đăng nhập tồn tại và phản hồi đúng hợp đồng trạng thái</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>api_functional</t>
+          <t>api_contract</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles -&gt; 401,403</t>
+          <t>POST /api/auth/login -&gt; 200,422</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.3-fe4ac4</t>
+          <t>TC-AC-1.2-2922e3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AC-1.3</t>
+          <t>AC-1.2, AC-1.9</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Gọi API activity polling không gây lỗi nhưng không coi là hoạt động người dùng theo PRD</t>
+          <t>Gọi API tạo lịch không có phiên đăng nhập bị từ chối</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1105,14 +1105,14 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>POST /api/auth/activity -&gt; 200</t>
+          <t>POST /api/run-schedules -&gt; 401,403</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.4-708e15</t>
+          <t>TC-AC-1.2-451131</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1122,17 +1122,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>AC-1.4</t>
+          <t>AC-1.2, AC-1.9</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Sau khi đăng xuất, token phiên bị thu hồi không thể gọi API được bảo vệ</t>
+          <t>Gọi API tạo lịch mà không có phiên hợp lệ nhận từ chối</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>flow</t>
+          <t>api_functional</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1147,19 +1147,19 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>POST /api/auth/logout -&gt; 200 | GET /api/auth/me -&gt; 401,403</t>
+          <t>POST /api/run-schedules -&gt; 401,403</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.5-53d829</t>
+          <t>TC-AC-1.2-c56c30</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AC-1.5</t>
+          <t>AC-1.2, AC-1.9</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu mới ngắn hơn 12 ký tự bị từ chối</t>
+          <t>Gọi API tạo filter profile (chức năng admin) khi chưa đăng nhập bị từ chối</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1199,14 +1199,14 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>POST /api/auth/password -&gt; 401,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.5-608b14</t>
+          <t>TC-AC-1.2-de66c4</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>AC-1.5</t>
+          <t>AC-1.2, AC-1.9</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Đổi mật khẩu mới trùng mật khẩu hiện tại bị từ chối</t>
+          <t>Gọi API quản trị không có phiên đăng nhập bị từ chối</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -1246,14 +1246,14 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>POST /api/auth/password -&gt; 401,422</t>
+          <t>GET /api/users -&gt; 401,403</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.6-73aa8f</t>
+          <t>TC-AC-1.3-fe4ac4</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AC-1.6</t>
+          <t>AC-1.3</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Tạo tài khoản với username rỗng bị từ chối</t>
+          <t>Gọi API activity polling không gây lỗi nhưng không coi là hoạt động người dùng theo PRD</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1293,14 +1293,14 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>POST /api/users -&gt; 401,403,422</t>
+          <t>POST /api/auth/activity -&gt; 200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.8-4b4505</t>
+          <t>TC-AC-1.4-6643f0</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1310,22 +1310,22 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>AC-1.8</t>
+          <t>AC-1.4</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Gọi API đổi timezone lịch khi không có phiên hợp lệ bị từ chối</t>
+          <t>Sau đăng xuất, gọi lại API được bảo vệ bị từ chối</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>api_functional</t>
+          <t>flow</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -1335,39 +1335,39 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>POST /api/run-schedules/time-zone -&gt; 401,403,422</t>
+          <t>POST /api/auth/logout -&gt; 200 | GET /api/users -&gt; 401,403</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-04506b</t>
+          <t>TC-AC-1.4-708e15</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>AC-2.1</t>
+          <t>AC-1.4</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Lấy danh sách filter profile khi chưa đăng nhập bị từ chối</t>
+          <t>Sau khi đăng xuất, token phiên bị thu hồi không thể gọi API được bảo vệ</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>api_functional</t>
+          <t>flow</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1382,34 +1382,34 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>GET /api/filter-profiles -&gt; 401,403</t>
+          <t>POST /api/auth/logout -&gt; 200 | GET /api/auth/me -&gt; 401,403</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-b65009</t>
+          <t>TC-AC-1.5-311fcd</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>AC-2.1</t>
+          <t>AC-1.5</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Update filter profile với revision sai bị từ chối</t>
+          <t>Đổi mật khẩu mới ngắn hơn 12 ký tự bị từ chối</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -1434,29 +1434,29 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>PUT /api/filter-profiles/{profile_id} -&gt; 401,403,422</t>
+          <t>POST /api/auth/password -&gt; 401,422</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-d2231e</t>
+          <t>TC-AC-1.5-53d829</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>AC-2.1</t>
+          <t>AC-1.5</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Tạo filter profile với tên trắng bị từ chối</t>
+          <t>Đổi mật khẩu mới ngắn hơn 12 ký tự bị từ chối</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1481,29 +1481,29 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
+          <t>POST /api/auth/password -&gt; 401,422</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-e57bad</t>
+          <t>TC-AC-1.5-608b14</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>AC-2.1</t>
+          <t>AC-1.5</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Tạo filter profile với tên vượt quá 120 ký tự bị từ chối</t>
+          <t>Đổi mật khẩu mới trùng mật khẩu hiện tại bị từ chối</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1528,29 +1528,29 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
+          <t>POST /api/auth/password -&gt; 401,422</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-12f73a</t>
+          <t>TC-AC-1.6-2cc1ca</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>AC-2.2</t>
+          <t>AC-1.6</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Tạo filter profile với values vượt quá giới hạn 100 bị từ chối</t>
+          <t>Reset mật khẩu quá ngắn bị từ chối theo giới hạn đầu vào</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1575,29 +1575,29 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
+          <t>POST /api/users/{username}/password -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-65e68a</t>
+          <t>TC-AC-1.6-73aa8f</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>AC-2.2</t>
+          <t>AC-1.6</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Tạo filter profile với năm sai kiểu dữ liệu bị từ chối</t>
+          <t>Tạo tài khoản với username rỗng bị từ chối</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1622,29 +1622,29 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
+          <t>POST /api/users -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-bc06cc</t>
+          <t>TC-AC-1.6-c46f21</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>AC-2.2</t>
+          <t>AC-1.6</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Tạo filter profile với định nghĩa ngoài schema bị từ chối</t>
+          <t>Tạo tài khoản với username rỗng bị từ chối</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -1669,29 +1669,29 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
+          <t>POST /api/users -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.4-fee573</t>
+          <t>TC-AC-1.7-852808</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>AC-2.4</t>
+          <t>AC-1.7</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Lấy option filter khi thiếu field hoặc tham số bắt buộc bị từ chối</t>
+          <t>Hạ role admin cuối cùng đang hoạt động bị từ chối</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -1716,29 +1716,29 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles/options -&gt; 401,403,422</t>
+          <t>PATCH /api/users/{username} -&gt; 401,403,404,422</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.7-336c2f</t>
+          <t>TC-AC-1.8-05da25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>AC-2.7</t>
+          <t>AC-1.8</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Tạo filter profile với field không hỗ trợ bị từ chối</t>
+          <t>Đổi múi giờ hiển thị sang giá trị không hợp lệ bị từ chối</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -1763,29 +1763,29 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
+          <t>POST /api/run-schedules/time-zone -&gt; 401,422</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.7-4e0f5e</t>
+          <t>TC-AC-1.8-4b4505</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>US-2</t>
+          <t>US-1</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>AC-2.7</t>
+          <t>AC-1.8</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Tạo filter profile với combination rule tự tham chiếu bị từ chối</t>
+          <t>Gọi API đổi timezone lịch khi không có phiên hợp lệ bị từ chối</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1810,14 +1810,14 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
+          <t>POST /api/run-schedules/time-zone -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.10-e03603</t>
+          <t>TC-AC-2.1-04506b</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>AC-2.10</t>
+          <t>AC-2.1</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Xóa filter profile với revision sai bị từ chối</t>
+          <t>Lấy danh sách filter profile khi chưa đăng nhập bị từ chối</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1857,29 +1857,29 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>DELETE /api/filter-profiles/{profile_id} -&gt; 401,403,422</t>
+          <t>GET /api/filter-profiles -&gt; 401,403</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.1-80daec</t>
+          <t>TC-AC-2.1-62b68a</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>US-3</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>AC-3.1</t>
+          <t>AC-2.1</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Tạo lịch với thời gian quá khứ bị từ chối</t>
+          <t>Tạo profile với tên trắng bị từ chối</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -1904,29 +1904,29 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.1-930e14</t>
+          <t>TC-AC-2.1-ab4267</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>US-3</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>AC-3.1</t>
+          <t>AC-2.1</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Tạo lịch thiếu timezone bị từ chối</t>
+          <t>Update profile với revision sai bị từ chối</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1951,29 +1951,29 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+          <t>PUT /api/filter-profiles/{profile_id} -&gt; 401,403,404,422</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.2-513705</t>
+          <t>TC-AC-2.1-b65009</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>US-3</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>AC-3.2</t>
+          <t>AC-2.1</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Tạo lịch với timezone không hỗ trợ bị từ chối</t>
+          <t>Update filter profile với revision sai bị từ chối</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1998,29 +1998,29 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+          <t>PUT /api/filter-profiles/{profile_id} -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.2-82804f</t>
+          <t>TC-AC-2.1-d2231e</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>US-3</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>AC-3.2</t>
+          <t>AC-2.1</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Tạo lịch với repeat kiểu daily bị từ chối</t>
+          <t>Tạo filter profile với tên trắng bị từ chối</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -2045,29 +2045,29 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.9-460ea9</t>
+          <t>TC-AC-2.1-e57bad</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>US-3</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>AC-3.9</t>
+          <t>AC-2.1</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Xóa lịch không tồn tại hoặc không đủ điều kiện bị từ chối</t>
+          <t>Tạo filter profile với tên vượt quá 120 ký tự bị từ chối</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2092,29 +2092,29 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>DELETE /api/run-schedules/{schedule_id} -&gt; 401,403,404,409,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.1-21fefc</t>
+          <t>TC-AC-2.1-eba453</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>US-4</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>AC-4.1</t>
+          <t>AC-2.1</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Claim case khi không có phiên runner hợp lệ bị từ chối</t>
+          <t>Tạo profile với tên vượt quá 120 ký tự bị từ chối</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -2139,29 +2139,29 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>POST /api/runner/queue/claim -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.3-887e73</t>
+          <t>TC-AC-2.2-005fab</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>US-4</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>AC-4.3</t>
+          <t>AC-2.2</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Preflight với job không tồn tại bị từ chối</t>
+          <t>Tạo profile với định nghĩa ngoài schema bị từ chối</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -2186,29 +2186,29 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>POST /api/ui-health/preflight -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.5-d2a564</t>
+          <t>TC-AC-2.2-12f73a</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>US-4</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>AC-4.5</t>
+          <t>AC-2.2</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Bắt đầu OCR với captchaId/challenge cũ hoặc job không tồn tại bị từ chối</t>
+          <t>Tạo filter profile với values vượt quá giới hạn 100 bị từ chối</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2233,29 +2233,29 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>POST /api/runner/ocr/start -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-5.1-d26c0e</t>
+          <t>TC-AC-2.2-364638</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>US-5</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>AC-5.1</t>
+          <t>AC-2.2</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Pause session không tồn tại bị từ chối</t>
+          <t>Tạo profile với năm sai kiểu dữ liệu bị từ chối</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -2280,29 +2280,29 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>POST /api/batch-queue/sessions/{session_id}/pause -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-5.2-26b392</t>
+          <t>TC-AC-2.2-65e68a</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>US-5</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>AC-5.2</t>
+          <t>AC-2.2</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Resume session không tồn tại bị từ chối</t>
+          <t>Tạo filter profile với năm sai kiểu dữ liệu bị từ chối</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2327,29 +2327,29 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>POST /api/batch-queue/sessions/{session_id}/resume -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.1-9bb102</t>
+          <t>TC-AC-2.2-bc06cc</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>US-6</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>AC-6.1</t>
+          <t>AC-2.2</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Xem báo cáo khi chưa có phiên hợp lệ bị từ chối</t>
+          <t>Tạo filter profile với định nghĩa ngoài schema bị từ chối</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2374,29 +2374,29 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>GET /api/annual-reports -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.4-09c6a0</t>
+          <t>TC-AC-2.4-7edcfd</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>US-6</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>AC-6.4</t>
+          <t>AC-2.4</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Yêu cầu phân trang vượt quá 100 dòng/trang bị từ chối hoặc giới hạn</t>
+          <t>Lấy filter options thiếu tham số bắt buộc bị từ chối</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -2421,29 +2421,29 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>GET /api/annual-reports -&gt; 401,403,422</t>
+          <t>POST /api/filter-profiles/options -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.6-9162d1</t>
+          <t>TC-AC-2.4-fee573</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>US-6</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>AC-6.6</t>
+          <t>AC-2.4</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Export filtered theo state cụ thể trả về dữ liệu khớp điều kiện</t>
+          <t>Lấy option filter khi thiếu field hoặc tham số bắt buộc bị từ chối</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -2468,29 +2468,29 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>GET /api/annual-reports/export -&gt; 401,403,404,422</t>
+          <t>POST /api/filter-profiles/options -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.7-310826</t>
+          <t>TC-AC-2.7-10ee24</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>US-6</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>AC-6.7</t>
+          <t>AC-2.7</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Export all thiếu confirmAll=true khi không có State/RTO search trả về lỗi xác nhận</t>
+          <t>Combination rule tự tham chiếu bị từ chối</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -2515,29 +2515,29 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>GET /api/annual-reports/export -&gt; 401,403,409,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.9-d21666</t>
+          <t>TC-AC-2.7-336c2f</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>US-6</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>AC-6.9</t>
+          <t>AC-2.7</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Export filtered không có dòng khớp trả về 404</t>
+          <t>Tạo filter profile với field không hỗ trợ bị từ chối</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -2562,29 +2562,29 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>GET /api/annual-reports/export -&gt; 401,403,404,422</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.1-7283a5</t>
+          <t>TC-AC-2.7-4e0f5e</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>US-7</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>AC-7.1</t>
+          <t>AC-2.7</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Run History chỉ admin xem, member hoặc chưa đăng nhập bị từ chối</t>
+          <t>Tạo filter profile với combination rule tự tham chiếu bị từ chối</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2609,29 +2609,29 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>GET /api/annual-reports/run-history -&gt; 401,403</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.5-57c3e3</t>
+          <t>TC-AC-2.7-c6ce4e</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>US-7</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>AC-7.5</t>
+          <t>AC-2.7</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>UI Health trạng thái trả về thông tin diagnostics</t>
+          <t>Trường không hỗ trợ trong include/exclude bị từ chối</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>GET /api/ui-health/status -&gt; 200</t>
+          <t>POST /api/filter-profiles -&gt; 401,403,422</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.7-0727b4</t>
+          <t>TC-AC-2.10-539375</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>US-7</t>
+          <t>US-2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>AC-7.7</t>
+          <t>AC-2.10</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>API audit chỉ admin truy cập, không có phiên hợp lệ bị từ chối</t>
+          <t>Xóa profile với revision sai bị từ chối</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -2703,54 +2703,1887 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>GET /api/audit -&gt; 401,403</t>
+          <t>DELETE /api/filter-profiles/{profile_id} -&gt; 401,403,404,422</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>TC-AC-2.10-d60cfe</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>US-2</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>AC-2.10</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Xóa profile thiếu tham số revision xác nhận bị từ chối</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>DELETE /api/filter-profiles/{profile_id} -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-2.10-e03603</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>US-2</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>AC-2.10</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Xóa filter profile với revision sai bị từ chối</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>DELETE /api/filter-profiles/{profile_id} -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-728a58</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.1</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Endpoint tạo lịch tồn tại và phản hồi đúng hợp đồng trạng thái</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>api_contract</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 201,401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-80daec</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.1</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch với thời gian quá khứ bị từ chối</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-930e14</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.1</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch thiếu timezone bị từ chối</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-93f265</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.1</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch thiếu timezone bị từ chối</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-c355da</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.1</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch với thời gian quá khứ bị từ chối</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-513705</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.2</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch với timezone không hỗ trợ bị từ chối</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-59bf6e</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.2</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch với múi giờ không được hỗ trợ bị từ chối</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-660311</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.2</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch once với timezone Asia/Kolkata hợp lệ được chấp nhận hoặc từ chối do profile không tồn tại</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-82804f</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.2</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch với repeat kiểu daily bị từ chối</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-8b1191</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.2</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Tạo lịch với repeat=daily bị từ chối</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/run-schedules -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.9-460ea9</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.9</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Xóa lịch không tồn tại hoặc không đủ điều kiện bị từ chối</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>DELETE /api/run-schedules/{schedule_id} -&gt; 401,403,404,409,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.9-596f7b</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>US-3</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>AC-3.9</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Xóa lịch không tồn tại bị từ chối phù hợp</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>DELETE /api/run-schedules/{schedule_id} -&gt; 401,403,404,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.1-21fefc</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>US-4</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>AC-4.1</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Claim case khi không có phiên runner hợp lệ bị từ chối</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/runner/queue/claim -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.1-c222b9</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>US-4</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>AC-4.1</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Claim case khi không có case khả dụng trả về trạng thái hợp lệ</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/runner/queue/claim -&gt; 401,403,200,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.3-39d7a8</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>US-4</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>AC-4.3</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Preflight thiếu dữ liệu đầu vào bị từ chối</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/ui-health/preflight -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.3-887e73</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>US-4</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>AC-4.3</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Preflight với job không tồn tại bị từ chối</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/ui-health/preflight -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.5-1b4163</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>US-4</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>AC-4.5</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Bắt đầu OCR với job/captchaId không hợp lệ bị từ chối</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/runner/ocr/start -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.5-d2a564</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>US-4</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>AC-4.5</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Bắt đầu OCR với captchaId/challenge cũ hoặc job không tồn tại bị từ chối</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/runner/ocr/start -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-5.1-d26c0e</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>US-5</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>AC-5.1</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Pause session không tồn tại bị từ chối</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/batch-queue/sessions/{session_id}/pause -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-5.1-fc0d6d</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>US-5</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>AC-5.1</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Pause session không tồn tại trả về lỗi phù hợp</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/batch-queue/sessions/{session_id}/pause -&gt; 401,403,404,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-5.2-26b392</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>US-5</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>AC-5.2</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Resume session không tồn tại bị từ chối</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/batch-queue/sessions/{session_id}/resume -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-5.2-d46430</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>US-5</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>AC-5.2</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Resume session không tồn tại trả về lỗi phù hợp</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>POST /api/batch-queue/sessions/{session_id}/resume -&gt; 401,403,404,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.1-9bb102</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.1</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Xem báo cáo khi chưa có phiên hợp lệ bị từ chối</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.1-a417d1</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.1</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Xem báo cáo với tham số year sai kiểu bị từ chối</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.4-09c6a0</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.4</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Yêu cầu phân trang vượt quá 100 dòng/trang bị từ chối hoặc giới hạn</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports -&gt; 401,403,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.6-7141b5</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.6</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Endpoint export báo cáo tồn tại và phản hồi đúng hợp đồng trạng thái</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>api_contract</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports/export -&gt; 200,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.6-9162d1</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.6</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Export filtered theo state cụ thể trả về dữ liệu khớp điều kiện</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports/export -&gt; 401,403,404,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.7-30fff6</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.7</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Export all thiếu confirmAll=true nhận 409</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports/export -&gt; 409</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.7-310826</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.7</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Export all thiếu confirmAll=true khi không có State/RTO search trả về lỗi xác nhận</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports/export -&gt; 401,403,409,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.9-d21666</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.9</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Export filtered không có dòng khớp trả về 404</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports/export -&gt; 401,403,404,422</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.9-fa7e6d</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>US-6</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>AC-6.9</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Export filtered không có dòng khớp trả về 404</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports/export -&gt; 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.1-1847df</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>US-7</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>AC-7.1</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Run History không có phiên admin bị từ chối</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports/run-history -&gt; 401,403</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.1-7283a5</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>US-7</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>AC-7.1</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Run History chỉ admin xem, member hoặc chưa đăng nhập bị từ chối</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/annual-reports/run-history -&gt; 401,403</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.5-57c3e3</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>US-7</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>AC-7.5</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>UI Health trạng thái trả về thông tin diagnostics</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/ui-health/status -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.7-0727b4</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>US-7</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>AC-7.7</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>API audit chỉ admin truy cập, không có phiên hợp lệ bị từ chối</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/audit -&gt; 401,403</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.7-348571</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>US-7</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>AC-7.7</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>API audit không có phiên admin bị từ chối</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/audit -&gt; 401,403</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
           <t>TC-AC-8.2-c375a7</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>US-8</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>AC-8.2</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Endpoint readiness trả về trạng thái sẵn sàng</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>api_functional</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>llm</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
         <is>
           <t>GET /api/ready -&gt; 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-8.3-d7ea61</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>US-8</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>AC-8.3</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Danh sách backup files yêu cầu quyền truy cập phù hợp</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>api_functional</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/files -&gt; 401,403</t>
         </is>
       </c>
     </row>
@@ -2779,7 +4612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2881,7 +4714,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.2-451131</t>
+          <t>TC-AC-1.1-c63e59</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2896,24 +4729,24 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>/api/run-schedules</t>
+          <t>/api/auth/login</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>{"profileId": "non-existent-profile", "repeat": "once", "scheduledAt": "2099-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
+          <t>{"password": "wrongpass123", "username": "nonexistent_user_zzz"}</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>401, 403</t>
+          <t>401, 422</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.2-c56c30</t>
+          <t>TC-AC-1.1-ff58e7</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2928,24 +4761,19 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>{"definitionVersion": 1, "name": "should-fail"}</t>
+          <t>/api/auth/login</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>401, 403</t>
+          <t>200, 422</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.3-fe4ac4</t>
+          <t>TC-AC-1.2-2922e3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2960,19 +4788,24 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>/api/auth/activity</t>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>{"name": "schedule-x", "profileId": "nonexistent-profile", "repeat": "once", "startAt": "2099-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>401, 403</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.4-708e15</t>
+          <t>TC-AC-1.2-451131</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2987,34 +4820,44 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>/api/auth/logout</t>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "non-existent-profile", "repeat": "once", "scheduledAt": "2099-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>401, 403</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.4-708e15</t>
+          <t>TC-AC-1.2-c56c30</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>/api/auth/me</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>{"definitionVersion": 1, "name": "should-fail"}</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -3026,7 +4869,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.5-53d829</t>
+          <t>TC-AC-1.2-de66c4</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3036,29 +4879,24 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>/api/auth/password</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>{"currentPassword": "oldpassword123", "newPassword": "short"}</t>
+          <t>/api/users</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>401, 422</t>
+          <t>401, 403</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.5-608b14</t>
+          <t>TC-AC-1.3-fe4ac4</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3073,24 +4911,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>/api/auth/password</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>{"currentPassword": "samepassword123", "newPassword": "samepassword123"}</t>
+          <t>/api/auth/activity</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>401, 422</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.6-73aa8f</t>
+          <t>TC-AC-1.4-6643f0</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3105,56 +4938,46 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>/api/users</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>{"password": "validpassword123", "role": "member", "username": ""}</t>
+          <t>/api/auth/logout</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.8-4b4505</t>
+          <t>TC-AC-1.4-6643f0</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>/api/run-schedules/time-zone</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>{"timezone": "Asia/Ho_Chi_Minh"}</t>
+          <t>/api/users</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 403</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-04506b</t>
+          <t>TC-AC-1.4-708e15</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3164,61 +4987,51 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
+          <t>/api/auth/logout</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>401, 403</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-b65009</t>
+          <t>TC-AC-1.4-708e15</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles/{profile_id}</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>{"profile_id": "non-existent-profile-id"}</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>{"definition": {}, "definitionVersion": 9999, "name": "Update revision test"}</t>
+          <t>/api/auth/me</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 403</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-d2231e</t>
+          <t>TC-AC-1.5-311fcd</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3233,24 +5046,24 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
+          <t>/api/auth/password</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>{"definition": {}, "definitionVersion": 1, "name": ""}</t>
+          <t>{"currentPassword": "oldpass123456", "newPassword": "short"}</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 422</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-e57bad</t>
+          <t>TC-AC-1.5-53d829</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3265,24 +5078,24 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
+          <t>/api/auth/password</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>{"definition": {}, "definitionVersion": 1, "name": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa"}</t>
+          <t>{"currentPassword": "oldpassword123", "newPassword": "short"}</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 422</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-12f73a</t>
+          <t>TC-AC-1.5-608b14</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3297,24 +5110,24 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
+          <t>/api/auth/password</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>{"definition": {"calendarYear": 2024, "filters": [{"field": "State", "mode": "fixed", "values": ["v1", "v2", "v3", "v4", "v5", "v6", "v7", "v8", "v9", "v10", "v11", "v12", "v13", "v14", "v15", "v16", "v17", "v18", "v19", "v20", "v21", "v22", "v23", "v24", "v25", "v26", "v27", "v28", "v29", "v30", "v31", "v32", "v33", "v34", "v35", "v36", "v37", "v38", "v39", "v40", "v41", "v42", "v43", "v44", "v45", "v46", "v47", "v48", "v49", "v50", "v51", "v52", "v53", "v54", "v55", "v56", "v57", "v58", "v59", "v60", "v61", "v62", "v63", "v64", "v65", "v66", "v67", "v68", "v69", "v70", "v71", "v72", "v73", "v74", "v75", "v76", "v77", "v78", "v79", "v80", "v81", "v82", "v83", "v84", "v85", "v86", "v87", "v88", "v89", "v90", "v91", "v92", "v93", "v94", "v95", "v96", "v97", "v98", "v99", "v100", "v101"]}], "xAxis": "MonthWise", "yAxis": "Maker"}, "definitionVersion": 1, "name": "Exceed values limit"}</t>
+          <t>{"currentPassword": "samepassword123", "newPassword": "samepassword123"}</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 422</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-65e68a</t>
+          <t>TC-AC-1.6-2cc1ca</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3329,12 +5142,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
+          <t>/api/users/{username}/password</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>{"username": "nonexistent_user"}</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>{"definition": {"calendarYear": "not-a-number", "xAxis": "MonthWise", "yAxis": "Maker"}, "definitionVersion": 1, "name": "Invalid year profile"}</t>
+          <t>{"newPassword": "short"}</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -3346,7 +5164,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-bc06cc</t>
+          <t>TC-AC-1.6-73aa8f</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3361,12 +5179,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
+          <t>/api/users</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>{"definition": {"unknownField": "value"}, "definitionVersion": 1, "name": "Invalid schema profile"}</t>
+          <t>{"password": "validpassword123", "role": "member", "username": ""}</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -3378,7 +5196,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.4-fee573</t>
+          <t>TC-AC-1.6-c46f21</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3393,12 +5211,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles/options</t>
+          <t>/api/users</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>{"field": "State", "parentValues": {}}</t>
+          <t>{"password": "somepassword1234", "role": "member", "username": ""}</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3410,7 +5228,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.7-336c2f</t>
+          <t>TC-AC-1.7-852808</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3420,29 +5238,34 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
+          <t>/api/users/{username}</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>{"username": "last_admin_example"}</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>{"definition": {"calendarYear": 2024, "filters": [{"field": "UnsupportedFieldXYZ", "mode": "fixed", "values": ["a"]}], "xAxis": "MonthWise", "yAxis": "Maker"}, "definitionVersion": 1, "name": "Unsupported field rule"}</t>
+          <t>{"role": "member"}</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 403, 404, 422</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.7-4e0f5e</t>
+          <t>TC-AC-1.8-05da25</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3457,24 +5280,24 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles</t>
+          <t>/api/run-schedules/time-zone</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>{"definition": {"calendarYear": 2024, "combinationRules": [{"field": "State", "refersTo": "State", "type": "require"}], "xAxis": "MonthWise", "yAxis": "Maker"}, "definitionVersion": 1, "name": "Self ref rule"}</t>
+          <t>{"timezone": "Invalid/Zone"}</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 422</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.10-e03603</t>
+          <t>TC-AC-1.8-4b4505</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3484,22 +5307,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>/api/filter-profiles/{profile_id}</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>{"profile_id": "non-existent-profile-id"}</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>{"revision": 999}</t>
+          <t>/api/run-schedules/time-zone</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>{"timezone": "Asia/Ho_Chi_Minh"}</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -3511,7 +5329,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.1-80daec</t>
+          <t>TC-AC-2.1-04506b</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3521,29 +5339,24 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>/api/run-schedules</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>{"profileId": "some-profile", "repeat": "once", "scheduledAt": "2020-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
+          <t>/api/filter-profiles</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 403</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.1-930e14</t>
+          <t>TC-AC-2.1-62b68a</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3558,12 +5371,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>/api/run-schedules</t>
+          <t>/api/filter-profiles</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>{"profileId": "some-profile", "repeat": "once", "scheduledAt": "2099-01-01T00:00:00"}</t>
+          <t>{"definition": {"xAxis": "MonthWise", "yAxis": "Maker", "year": 2024}, "name": ""}</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3575,7 +5388,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.2-513705</t>
+          <t>TC-AC-2.1-ab4267</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3585,29 +5398,34 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>/api/run-schedules</t>
+          <t>/api/filter-profiles/{profile_id}</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>{"profile_id": "nonexistent-profile-id"}</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>{"profileId": "some-profile", "repeat": "once", "scheduledAt": "2099-01-01T00:00:00+05:30", "timezone": "Europe/London"}</t>
+          <t>{"definition": {"xAxis": "MonthWise", "yAxis": "Maker", "year": 2024}, "name": "updated-name", "revision": 999999}</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 422</t>
+          <t>401, 403, 404, 422</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.2-82804f</t>
+          <t>TC-AC-2.1-b65009</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3617,17 +5435,22 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>/api/run-schedules</t>
+          <t>/api/filter-profiles/{profile_id}</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>{"profile_id": "non-existent-profile-id"}</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>{"profileId": "some-profile", "repeat": "daily", "scheduledAt": "2099-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
+          <t>{"definition": {}, "definitionVersion": 9999, "name": "Update revision test"}</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -3639,7 +5462,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.9-460ea9</t>
+          <t>TC-AC-2.1-d2231e</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3649,29 +5472,29 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>/api/run-schedules/{schedule_id}</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>{"schedule_id": "non-existent-schedule-id"}</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {}, "definitionVersion": 1, "name": ""}</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 404, 409, 422</t>
+          <t>401, 403, 422</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.1-21fefc</t>
+          <t>TC-AC-2.1-e57bad</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3686,7 +5509,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>/api/runner/queue/claim</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {}, "definitionVersion": 1, "name": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa"}</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -3698,7 +5526,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.3-887e73</t>
+          <t>TC-AC-2.1-eba453</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3713,12 +5541,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>/api/ui-health/preflight</t>
+          <t>/api/filter-profiles</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>{"contractVersion": "v1", "jobId": "non-existent-job"}</t>
+          <t>{"definition": {"xAxis": "MonthWise", "yAxis": "Maker", "year": 2024}, "name": "aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa"}</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -3730,7 +5558,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.5-d2a564</t>
+          <t>TC-AC-2.2-005fab</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3745,12 +5573,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>/api/runner/ocr/start</t>
+          <t>/api/filter-profiles</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>{"captchaId": "old-challenge-id", "jobId": "non-existent-job"}</t>
+          <t>{"definition": {"unsupportedField": true, "xAxis": "MonthWise", "yAxis": "Maker", "year": 2024}, "name": "bad-schema-profile"}</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -3762,7 +5590,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-5.1-d26c0e</t>
+          <t>TC-AC-2.2-12f73a</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3777,12 +5605,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>/api/batch-queue/sessions/{session_id}/pause</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>{"session_id": "non-existent-session-id"}</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {"calendarYear": 2024, "filters": [{"field": "State", "mode": "fixed", "values": ["v1", "v2", "v3", "v4", "v5", "v6", "v7", "v8", "v9", "v10", "v11", "v12", "v13", "v14", "v15", "v16", "v17", "v18", "v19", "v20", "v21", "v22", "v23", "v24", "v25", "v26", "v27", "v28", "v29", "v30", "v31", "v32", "v33", "v34", "v35", "v36", "v37", "v38", "v39", "v40", "v41", "v42", "v43", "v44", "v45", "v46", "v47", "v48", "v49", "v50", "v51", "v52", "v53", "v54", "v55", "v56", "v57", "v58", "v59", "v60", "v61", "v62", "v63", "v64", "v65", "v66", "v67", "v68", "v69", "v70", "v71", "v72", "v73", "v74", "v75", "v76", "v77", "v78", "v79", "v80", "v81", "v82", "v83", "v84", "v85", "v86", "v87", "v88", "v89", "v90", "v91", "v92", "v93", "v94", "v95", "v96", "v97", "v98", "v99", "v100", "v101"]}], "xAxis": "MonthWise", "yAxis": "Maker"}, "definitionVersion": 1, "name": "Exceed values limit"}</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -3794,7 +5622,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-5.2-26b392</t>
+          <t>TC-AC-2.2-364638</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3809,12 +5637,12 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>/api/batch-queue/sessions/{session_id}/resume</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>{"session_id": "non-existent-session-id"}</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {"xAxis": "MonthWise", "yAxis": "Maker", "year": "not-a-number"}, "name": "bad-year-profile"}</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -3826,7 +5654,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.1-9bb102</t>
+          <t>TC-AC-2.2-65e68a</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3836,17 +5664,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>/api/annual-reports</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>{"dataset": "vehicles", "year": 2024}</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {"calendarYear": "not-a-number", "xAxis": "MonthWise", "yAxis": "Maker"}, "definitionVersion": 1, "name": "Invalid year profile"}</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -3858,7 +5686,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.4-09c6a0</t>
+          <t>TC-AC-2.2-bc06cc</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3868,17 +5696,17 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>/api/annual-reports</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>{"dataset": "vehicles", "page": 1, "pageSize": 101, "year": 2024}</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {"unknownField": "value"}, "definitionVersion": 1, "name": "Invalid schema profile"}</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -3890,7 +5718,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.6-9162d1</t>
+          <t>TC-AC-2.4-7edcfd</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3900,29 +5728,24 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>/api/annual-reports/export</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>{"dataset": "vehicles", "state": "SomeState", "year": 2024}</t>
+          <t>/api/filter-profiles/options</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 404, 422</t>
+          <t>401, 403, 422</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.7-310826</t>
+          <t>TC-AC-2.4-fee573</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3932,29 +5755,29 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>/api/annual-reports/export</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>{"dataset": "vehicles", "year": 2024}</t>
+          <t>/api/filter-profiles/options</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>{"field": "State", "parentValues": {}}</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 409, 422</t>
+          <t>401, 403, 422</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.9-d21666</t>
+          <t>TC-AC-2.7-10ee24</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3964,29 +5787,29 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>/api/annual-reports/export</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>{"confirmAll": false, "dataset": "vehicles", "state": "NonExistentStateXYZ123", "year": 2024}</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {"combinationRules": [{"field": "State", "ref": "State", "type": "require"}], "xAxis": "MonthWise", "yAxis": "Maker", "year": 2024}, "name": "self-ref-rule"}</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>401, 403, 404, 422</t>
+          <t>401, 403, 422</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.1-7283a5</t>
+          <t>TC-AC-2.7-336c2f</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3996,24 +5819,29 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>/api/annual-reports/run-history</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {"calendarYear": 2024, "filters": [{"field": "UnsupportedFieldXYZ", "mode": "fixed", "values": ["a"]}], "xAxis": "MonthWise", "yAxis": "Maker"}, "definitionVersion": 1, "name": "Unsupported field rule"}</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>401, 403</t>
+          <t>401, 403, 422</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.5-57c3e3</t>
+          <t>TC-AC-2.7-4e0f5e</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4023,24 +5851,29 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>/api/ui-health/status</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {"calendarYear": 2024, "combinationRules": [{"field": "State", "refersTo": "State", "type": "require"}], "xAxis": "MonthWise", "yAxis": "Maker"}, "definitionVersion": 1, "name": "Self ref rule"}</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>401, 403, 422</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.7-0727b4</t>
+          <t>TC-AC-2.7-c6ce4e</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -4050,44 +5883,1284 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>/api/audit</t>
+          <t>/api/filter-profiles</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>{"definition": {"include": {"UnsupportedField": ["x"]}, "xAxis": "MonthWise", "yAxis": "Maker", "year": 2024}, "name": "unsupported-field-rule"}</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>401, 403</t>
+          <t>401, 403, 422</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>TC-AC-2.10-539375</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>/api/filter-profiles/{profile_id}</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>{"profile_id": "nonexistent-profile-id"}</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>{"revision": 999999}</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 404, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-2.10-d60cfe</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>/api/filter-profiles/{profile_id}</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>{"profile_id": "nonexistent-profile-id"}</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-2.10-e03603</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>/api/filter-profiles/{profile_id}</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>{"profile_id": "non-existent-profile-id"}</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>{"revision": 999}</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-728a58</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>201, 401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-80daec</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "some-profile", "repeat": "once", "scheduledAt": "2020-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-930e14</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "some-profile", "repeat": "once", "scheduledAt": "2099-01-01T00:00:00"}</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-93f265</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "nonexistent-profile", "repeat": "once", "startAt": "2099-01-01T00:00:00"}</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.1-c355da</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "nonexistent-profile", "repeat": "once", "startAt": "2000-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-513705</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "some-profile", "repeat": "once", "scheduledAt": "2099-01-01T00:00:00+05:30", "timezone": "Europe/London"}</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-59bf6e</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "nonexistent-profile", "repeat": "once", "startAt": "2099-01-01T00:00:00+00:00", "timezone": "UTC"}</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-660311</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "nonexistent-profile", "repeat": "once", "startAt": "2099-01-01T00:00:00+05:30", "timezone": "Asia/Kolkata"}</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-82804f</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "some-profile", "repeat": "daily", "scheduledAt": "2099-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.2-8b1191</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>{"profileId": "nonexistent-profile", "repeat": "daily", "startAt": "2099-01-01T00:00:00+07:00", "timezone": "Asia/Ho_Chi_Minh"}</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.9-460ea9</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules/{schedule_id}</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>{"schedule_id": "non-existent-schedule-id"}</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 404, 409, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-3.9-596f7b</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>/api/run-schedules/{schedule_id}</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>{"schedule_id": "nonexistent-schedule-id"}</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 404, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.1-21fefc</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>/api/runner/queue/claim</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.1-c222b9</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>/api/runner/queue/claim</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 200, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.3-39d7a8</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>/api/ui-health/preflight</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.3-887e73</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>/api/ui-health/preflight</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>{"contractVersion": "v1", "jobId": "non-existent-job"}</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.5-1b4163</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>/api/runner/ocr/start</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>{"captchaId": "nonexistent-captcha", "jobId": "nonexistent-job"}</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-4.5-d2a564</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>/api/runner/ocr/start</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>{"captchaId": "old-challenge-id", "jobId": "non-existent-job"}</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-5.1-d26c0e</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>/api/batch-queue/sessions/{session_id}/pause</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>{"session_id": "non-existent-session-id"}</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-5.1-fc0d6d</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>/api/batch-queue/sessions/{session_id}/pause</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>{"session_id": "nonexistent-session-id"}</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 404, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-5.2-26b392</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>/api/batch-queue/sessions/{session_id}/resume</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>{"session_id": "non-existent-session-id"}</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-5.2-d46430</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>/api/batch-queue/sessions/{session_id}/resume</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>{"session_id": "nonexistent-session-id"}</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 404, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.1-9bb102</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>{"dataset": "vehicles", "year": 2024}</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.1-a417d1</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>{"year": "invalid-year"}</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.4-09c6a0</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>{"dataset": "vehicles", "page": 1, "pageSize": 101, "year": 2024}</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.6-7141b5</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports/export</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>200, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.6-9162d1</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports/export</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>{"dataset": "vehicles", "state": "SomeState", "year": 2024}</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 404, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.7-30fff6</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports/export</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>{"dataset": "default", "year": 2024}</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.7-310826</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports/export</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>{"dataset": "vehicles", "year": 2024}</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 409, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.9-d21666</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports/export</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>{"confirmAll": false, "dataset": "vehicles", "state": "NonExistentStateXYZ123", "year": 2024}</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>401, 403, 404, 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.9-fa7e6d</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports/export</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>{"confirmAll": false, "dataset": "default", "state": "NonExistentStateZZZ", "year": 2024}</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.1-1847df</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports/run-history</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>401, 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.1-7283a5</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>/api/annual-reports/run-history</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>401, 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.5-57c3e3</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>/api/ui-health/status</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.7-0727b4</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>/api/audit</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>401, 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.7-348571</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>/api/audit</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>401, 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
           <t>TC-AC-8.2-c375a7</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>/api/ready</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="I80" s="3" t="inlineStr">
         <is>
           <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-8.3-d7ea61</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>/api/files</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>401, 403</t>
         </is>
       </c>
     </row>
@@ -4107,7 +7180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4196,7 +7269,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.2-451131</t>
+          <t>TC-AC-1.1-c63e59</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -4211,29 +7284,29 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$.ok</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>eq</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>boolean</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.2-c56c30</t>
+          <t>TC-AC-1.1-c63e59</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -4243,12 +7316,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$.status</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -4258,19 +7331,19 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.3-fe4ac4</t>
+          <t>TC-AC-1.2-451131</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -4307,7 +7380,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.4-708e15</t>
+          <t>TC-AC-1.2-c56c30</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -4344,12 +7417,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.4-708e15</t>
+          <t>TC-AC-1.2-de66c4</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -4359,7 +7432,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$.status</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -4369,19 +7442,19 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.5-53d829</t>
+          <t>TC-AC-1.3-fe4ac4</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4418,12 +7491,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.5-608b14</t>
+          <t>TC-AC-1.4-6643f0</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -4433,7 +7506,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$.status</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4443,19 +7516,19 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.6-73aa8f</t>
+          <t>TC-AC-1.4-708e15</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -4492,12 +7565,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.8-4b4505</t>
+          <t>TC-AC-1.4-708e15</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -4529,7 +7602,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-04506b</t>
+          <t>TC-AC-1.5-311fcd</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -4544,7 +7617,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$.status</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -4554,19 +7627,19 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-b65009</t>
+          <t>TC-AC-1.5-53d829</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -4603,7 +7676,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-d2231e</t>
+          <t>TC-AC-1.5-608b14</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -4640,7 +7713,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-e57bad</t>
+          <t>TC-AC-1.6-73aa8f</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -4677,7 +7750,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-12f73a</t>
+          <t>TC-AC-1.6-c46f21</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -4692,7 +7765,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$.status</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -4702,19 +7775,19 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>201</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-65e68a</t>
+          <t>TC-AC-1.8-4b4505</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -4751,7 +7824,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.2-bc06cc</t>
+          <t>TC-AC-2.1-04506b</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4788,7 +7861,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.4-fee573</t>
+          <t>TC-AC-2.1-62b68a</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4803,7 +7876,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$.status</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -4813,19 +7886,19 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.7-336c2f</t>
+          <t>TC-AC-2.1-b65009</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4862,7 +7935,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.7-4e0f5e</t>
+          <t>TC-AC-2.1-d2231e</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4899,7 +7972,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.10-e03603</t>
+          <t>TC-AC-2.1-e57bad</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4936,7 +8009,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.1-80daec</t>
+          <t>TC-AC-2.2-12f73a</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -4973,7 +8046,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.1-930e14</t>
+          <t>TC-AC-2.2-65e68a</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5010,7 +8083,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.2-513705</t>
+          <t>TC-AC-2.2-bc06cc</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5047,7 +8120,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.2-82804f</t>
+          <t>TC-AC-2.4-fee573</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5084,7 +8157,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.9-460ea9</t>
+          <t>TC-AC-2.7-336c2f</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -5121,7 +8194,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.1-21fefc</t>
+          <t>TC-AC-2.7-4e0f5e</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -5158,7 +8231,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.3-887e73</t>
+          <t>TC-AC-2.10-e03603</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -5195,7 +8268,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.5-d2a564</t>
+          <t>TC-AC-3.1-80daec</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -5232,7 +8305,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-5.1-d26c0e</t>
+          <t>TC-AC-3.1-930e14</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -5269,7 +8342,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-5.2-26b392</t>
+          <t>TC-AC-3.2-513705</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -5306,7 +8379,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.1-9bb102</t>
+          <t>TC-AC-3.2-82804f</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -5343,7 +8416,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.4-09c6a0</t>
+          <t>TC-AC-3.9-460ea9</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -5380,7 +8453,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.6-9162d1</t>
+          <t>TC-AC-4.1-21fefc</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -5417,7 +8490,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.7-310826</t>
+          <t>TC-AC-4.3-887e73</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -5454,7 +8527,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-6.9-d21666</t>
+          <t>TC-AC-4.5-d2a564</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -5491,7 +8564,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.1-7283a5</t>
+          <t>TC-AC-5.1-d26c0e</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -5528,7 +8601,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.5-57c3e3</t>
+          <t>TC-AC-5.2-26b392</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -5565,7 +8638,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-7.7-0727b4</t>
+          <t>TC-AC-6.1-9bb102</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -5602,35 +8675,368 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>TC-AC-6.4-09c6a0</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.6-9162d1</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.7-30fff6</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>$.status</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.7-310826</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.9-d21666</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-6.9-fa7e6d</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>$.status</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.1-7283a5</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.5-57c3e3</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-7.7-0727b4</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>TC-AC-8.2-c375a7</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>$</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>ne</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>null</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>null</t>
         </is>
@@ -6308,7 +9714,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-1</t>
+          <t>approved 1, draft 2, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6330,7 +9736,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>approved 2, draft 0, rejected 0; story US-1</t>
+          <t>approved 2, draft 2, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6374,7 +9780,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-1</t>
+          <t>approved 1, draft 1, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6396,7 +9802,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>approved 2, draft 0, rejected 0; story US-1</t>
+          <t>approved 2, draft 1, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6418,7 +9824,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-1</t>
+          <t>approved 1, draft 2, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6435,12 +9841,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 0, rejected 0; story US-1</t>
+          <t>approved 0, draft 1, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6462,7 +9868,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-1</t>
+          <t>approved 1, draft 1, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6484,7 +9890,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>approved 2, draft 0, rejected 0; story US-1</t>
+          <t>approved 2, draft 2, rejected 0; story US-1</t>
         </is>
       </c>
     </row>
@@ -6506,7 +9912,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>approved 4, draft 0, rejected 0; story US-2</t>
+          <t>approved 4, draft 3, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6528,7 +9934,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>approved 3, draft 0, rejected 0; story US-2</t>
+          <t>approved 3, draft 2, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6572,7 +9978,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-2</t>
+          <t>approved 1, draft 1, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6638,7 +10044,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>approved 2, draft 0, rejected 0; story US-2</t>
+          <t>approved 2, draft 2, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6704,7 +10110,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-2</t>
+          <t>approved 1, draft 2, rejected 0; story US-2</t>
         </is>
       </c>
     </row>
@@ -6748,7 +10154,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>approved 2, draft 0, rejected 0; story US-3</t>
+          <t>approved 2, draft 3, rejected 0; story US-3</t>
         </is>
       </c>
     </row>
@@ -6770,7 +10176,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>approved 2, draft 0, rejected 0; story US-3</t>
+          <t>approved 2, draft 3, rejected 0; story US-3</t>
         </is>
       </c>
     </row>
@@ -6924,7 +10330,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-3</t>
+          <t>approved 1, draft 1, rejected 0; story US-3</t>
         </is>
       </c>
     </row>
@@ -6946,7 +10352,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-4</t>
+          <t>approved 1, draft 1, rejected 0; story US-4</t>
         </is>
       </c>
     </row>
@@ -6990,7 +10396,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-4</t>
+          <t>approved 1, draft 1, rejected 0; story US-4</t>
         </is>
       </c>
     </row>
@@ -7034,7 +10440,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-4</t>
+          <t>approved 1, draft 1, rejected 0; story US-4</t>
         </is>
       </c>
     </row>
@@ -7166,7 +10572,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-5</t>
+          <t>approved 1, draft 1, rejected 0; story US-5</t>
         </is>
       </c>
     </row>
@@ -7188,7 +10594,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-5</t>
+          <t>approved 1, draft 1, rejected 0; story US-5</t>
         </is>
       </c>
     </row>
@@ -7342,7 +10748,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-6</t>
+          <t>approved 1, draft 1, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7452,7 +10858,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-6</t>
+          <t>approved 1, draft 1, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7474,7 +10880,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-6</t>
+          <t>approved 1, draft 1, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7518,7 +10924,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-6</t>
+          <t>approved 1, draft 1, rejected 0; story US-6</t>
         </is>
       </c>
     </row>
@@ -7606,7 +11012,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-7</t>
+          <t>approved 1, draft 1, rejected 0; story US-7</t>
         </is>
       </c>
     </row>
@@ -7738,7 +11144,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>approved 1, draft 0, rejected 0; story US-7</t>
+          <t>approved 1, draft 1, rejected 0; story US-7</t>
         </is>
       </c>
     </row>
@@ -7799,12 +11205,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>approved 0, draft 0, rejected 0; story US-8</t>
+          <t>approved 0, draft 1, rejected 0; story US-8</t>
         </is>
       </c>
     </row>
@@ -9541,7 +12947,7 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.4-708e15</t>
+          <t>TC-AC-1.4-6643f0, TC-AC-1.4-708e15</t>
         </is>
       </c>
     </row>
@@ -10401,7 +13807,7 @@
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-2.1-d2231e</t>
+          <t>TC-AC-2.1-62b68a, TC-AC-2.1-d2231e</t>
         </is>
       </c>
     </row>
@@ -11081,7 +14487,12 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>covered</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-2.10-d60cfe</t>
         </is>
       </c>
     </row>
@@ -12638,7 +16049,7 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-3.2-82804f</t>
+          <t>TC-AC-3.2-82804f, TC-AC-3.2-8b1191</t>
         </is>
       </c>
     </row>
@@ -12796,7 +16207,7 @@
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.8-4b4505</t>
+          <t>TC-AC-1.8-05da25, TC-AC-1.8-4b4505</t>
         </is>
       </c>
     </row>
@@ -13838,7 +17249,7 @@
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-4.3-887e73</t>
+          <t>TC-AC-4.3-39d7a8, TC-AC-4.3-887e73</t>
         </is>
       </c>
     </row>
@@ -14171,7 +17582,7 @@
       </c>
       <c r="D441" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.6-73aa8f</t>
+          <t>TC-AC-1.6-73aa8f, TC-AC-1.6-c46f21</t>
         </is>
       </c>
     </row>
@@ -14261,7 +17672,7 @@
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.6-73aa8f</t>
+          <t>TC-AC-1.6-73aa8f, TC-AC-1.6-c46f21</t>
         </is>
       </c>
     </row>
@@ -14283,7 +17694,7 @@
       </c>
       <c r="D447" s="3" t="inlineStr">
         <is>
-          <t>TC-AC-1.6-73aa8f</t>
+          <t>TC-AC-1.6-73aa8f, TC-AC-1.6-c46f21</t>
         </is>
       </c>
     </row>
@@ -14334,7 +17745,12 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>covered</t>
+        </is>
+      </c>
+      <c r="D450" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-1.7-852808</t>
         </is>
       </c>
     </row>
@@ -14385,7 +17801,12 @@
       </c>
       <c r="C453" s="3" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>covered</t>
+        </is>
+      </c>
+      <c r="D453" s="3" t="inlineStr">
+        <is>
+          <t>TC-AC-1.6-2cc1ca</t>
         </is>
       </c>
     </row>
